--- a/AI_AuditLog_SWP_NguyenAnhMinh_DE190975.xlsx
+++ b/AI_AuditLog_SWP_NguyenAnhMinh_DE190975.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="45">
   <si>
     <t>Entry #</t>
   </si>
@@ -97,6 +97,9 @@
     <t>Hallucination Detected?: None.</t>
   </si>
   <si>
+    <t>Hallucination Detected?</t>
+  </si>
+  <si>
     <t>PROBLEM-SOLVING</t>
   </si>
   <si>
@@ -118,7 +121,7 @@
     <t>Bối cảnh dự án yêu cầu file tải lên phải được gửi trực tiếp cho AI xử lý. Nếu người dùng tải lên file ảnh (.jpg) hoặc file quá lớn (&gt;10MB), luồng AI phân tích phía sau sẽ bị crash và tốn chi phí server.</t>
   </si>
   <si>
-    <t>Tôi chỉ dùng cấu trúc UI của AI. Về mặt logic, tôi đã tự code thêm phần Validation trên Frontend: chặn cứng chỉ cho phép định dạng .pdf và dung lượng &lt; 5MB. Đồng thời, tôi tự viết RLS Policy trên Supabase để chỉ Authenticated Users mới được phép INSERT vào cv-bucket. Cuối cùng, tôi kết nối hàm upload onSuccess để tự động trigger API gọi AI phân tích điểm ATS, tạo thành một luồng khép kín.</t>
+    <t>Tôi chỉ dùng cấu trúc UI của AI. Về mặt logic, tôi đã tự code thêm phần Validation trên Frontend: chặn cứng chỉ cho phép định dạng .pdf và dung lượng &lt; 10MB. Đồng thời, tôi tự viết RLS Policy trên Supabase để chỉ Authenticated Users mới được phép INSERT vào cv-bucket. Cuối cùng, tôi kết nối hàm upload onSuccess để tự động trigger API gọi AI phân tích điểm ATS, tạo thành một luồng khép kín.</t>
   </si>
   <si>
     <t>Quyết định không phụ thuộc hoàn toàn vào code mẫu của AI. Tôi chọn cách tự xây dựng các lớp bảo mật (Validation file type/size và Supabase RLS) vì an toàn dữ liệu và tính ổn định của hệ thống quan trọng hơn việc code nhanh.</t>
@@ -128,6 +131,39 @@
   </si>
   <si>
     <t>Hallucination Detected?: Oversimplification.</t>
+  </si>
+  <si>
+    <t>PROBLEM-SOLVING &amp; PROMPT ENGINEERING</t>
+  </si>
+  <si>
+    <t>Implementation &amp; Testing (CV Analysis Module)</t>
+  </si>
+  <si>
+    <t>Module chấm điểm CV bằng AI hoạt động sai lệch nghiêm trọng. Nó chấm 88 điểm cho một CV "troll" (không có kỹ năng thực tế) và 8 điểm cho file DOCX trống, nhưng lại chấm 0 điểm cho một CV PDF chuẩn. Ngoài ra, file DOCX không hiển thị được preview trên UI.</t>
+  </si>
+  <si>
+    <t>"Train AI to analyze CVs thoroughly... A standard IT CV is evaluated by recruiters based on 5 core criteria: relevance to JD, project experience, professional skills, quantifiable achievements (STAR), and clarity of layout... if you receive another CV unrelated to IT, state 'Your CV is not related to IT'."</t>
+  </si>
+  <si>
+    <t>AI đã sửa lỗi trích xuất text cho PDF (pdfjs-dist) và DOCX (mammoth), đồng thời thêm tính năng preview HTML cho DOCX. AI cập nhật prompt hệ thống áp dụng thang điểm 5 tiêu chí IT khắt khe (JD 20%, Project 30%, Skills 20%, STAR 20%, Layout 10%), giảm temperature xuống 0.1 để bớt "sáng tạo", và thêm bộ lọc từ chối thẳng thừng các CV trống hoặc CV ngoài ngành IT.</t>
+  </si>
+  <si>
+    <t>Tôi phát hiện ra lỗ hổng tư duy của AI (Hallucination): nếu không có luật lệ rõ ràng, AI sẽ luôn cố gắng "làm hài lòng" người dùng bằng cách cho điểm cao (65-95) một cách vô lý kể cả khi file trống hoặc chứa nội dung rác. Tôi quyết định không thể tin tưởng vào prompt mặc định của AI.</t>
+  </si>
+  <si>
+    <t>Dựa trên kinh nghiệm và tiêu chuẩn tuyển dụng IT thực tế, tôi hiểu rằng các HR và Tech Lead đánh giá CV thông qua các từ khóa công nghệ, link GitHub, và đặc biệt là công thức STAR (Tình huống - Nhiệm vụ - Hành động - Kết quả). Hệ thống này sinh ra cho dân IT, nên nó phải hành xử như một chuyên gia IT độc miệng chứ không phải một AI dĩ hòa vi quý.</t>
+  </si>
+  <si>
+    <t>Thay vì chỉ bảo AI "hãy chấm gắt lên", tôi đã chủ động thiết kế và "dạy" (train) lại AI bằng một bộ khung 5 tiêu chí rõ ràng (Rubric). Đồng thời, tôi kết hợp xử lý logic ở tầng Frontend: yêu cầu kiểm tra độ dài text và format file (mammoth parsing) TRƯỚC KHI gửi lên Gemini, giúp lọc bỏ file rác ngay từ vòng gửi xe để tiết kiệm chi phí API.</t>
+  </si>
+  <si>
+    <t>Quyết định áp đặt quy tắc "Fail-fast" (Từ chối ngay lập tức): Nếu nhận diện CV thuộc ngành Kế toán, Marketing... hoặc file rỗng, hệ thống phải trả về thông báo lỗi "CV không liên quan đến IT" và chấm 0 điểm, tuyệt đối không cố gắng phân tích. Đây là quyết định cốt lõi giúp hệ thống của nhóm đáng tin cậy và chuyên nghiệp.</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0</t>
+  </si>
+  <si>
+    <t>Yes (Severe Hallucination &amp; Flawed Logic - AI tự bịa ra điểm số cao cho file trống và CV rác).</t>
   </si>
 </sst>
 </file>
@@ -170,6 +206,14 @@
     </font>
     <font>
       <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
@@ -191,14 +235,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
@@ -521,12 +557,40 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -630,28 +694,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -663,34 +727,34 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -775,23 +839,58 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -845,7 +944,7 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="39">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -859,6 +958,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <numFmt numFmtId="49" formatCode="@"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -873,6 +974,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <numFmt numFmtId="49" formatCode="@"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -887,6 +990,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <numFmt numFmtId="49" formatCode="@"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -901,6 +1006,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <numFmt numFmtId="49" formatCode="@"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -915,6 +1022,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <numFmt numFmtId="49" formatCode="@"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -929,6 +1038,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <numFmt numFmtId="49" formatCode="@"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -943,6 +1054,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <numFmt numFmtId="49" formatCode="@"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -957,6 +1070,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <numFmt numFmtId="49" formatCode="@"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -971,6 +1086,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <numFmt numFmtId="49" formatCode="@"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -985,6 +1102,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <numFmt numFmtId="49" formatCode="@"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -999,6 +1118,8 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <numFmt numFmtId="49" formatCode="@"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -1013,6 +1134,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <alignment vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -1027,6 +1149,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <alignment vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -1041,6 +1164,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <alignment vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -1055,6 +1179,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <alignment vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -1069,6 +1194,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <alignment vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -1083,6 +1209,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <alignment vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -1097,6 +1224,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <alignment vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -1111,6 +1239,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <alignment vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -1125,6 +1254,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <alignment vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
@@ -1139,11 +1269,184 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
       </font>
+      <alignment vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
         <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1196,11 +1499,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="AI_AuditLog_SWP_Template-style" pivot="0" count="4" xr9:uid="{8D18406F-9D62-44FF-9C2A-9DCA38486D1A}">
-      <tableStyleElement type="wholeTable" dxfId="25"/>
-      <tableStyleElement type="headerRow" dxfId="24"/>
-      <tableStyleElement type="firstRowStripe" dxfId="23"/>
-      <tableStyleElement type="secondRowStripe" dxfId="22"/>
+    <tableStyle name="AI_AuditLog_SWP_Template-style" pivot="0" count="4" xr9:uid="{3D066CE8-E913-42A9-9BED-7C92F5D4FDC9}">
+      <tableStyleElement type="wholeTable" dxfId="38"/>
+      <tableStyleElement type="headerRow" dxfId="37"/>
+      <tableStyleElement type="firstRowStripe" dxfId="36"/>
+      <tableStyleElement type="secondRowStripe" dxfId="35"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1231,8 +1534,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SWP_3" displayName="SWP_3" ref="A1:K4">
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SWP_3" displayName="SWP_3" ref="A1:L4">
+  <tableColumns count="12">
     <tableColumn id="1" name="Entry #" dataDxfId="11"/>
     <tableColumn id="2" name="Prompt Type" dataDxfId="12"/>
     <tableColumn id="3" name="Stage/Component" dataDxfId="13"/>
@@ -1244,6 +1547,27 @@
     <tableColumn id="9" name="Human Delta: Creative Synthesis" dataDxfId="19"/>
     <tableColumn id="10" name="Human Delta: Decision Ownership" dataDxfId="20"/>
     <tableColumn id="11" name="Evidence" dataDxfId="21"/>
+    <tableColumn id="12" name="Hallucination Detected?" dataDxfId="22"/>
+  </tableColumns>
+  <tableStyleInfo name="AI_AuditLog_SWP_Template-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SWP_34" displayName="SWP_34" ref="A1:L4">
+  <tableColumns count="12">
+    <tableColumn id="1" name="Entry #" dataDxfId="23"/>
+    <tableColumn id="2" name="Prompt Type" dataDxfId="24"/>
+    <tableColumn id="3" name="Stage/Component" dataDxfId="25"/>
+    <tableColumn id="4" name="Problem/Context" dataDxfId="26"/>
+    <tableColumn id="5" name="Prompt to AI" dataDxfId="27"/>
+    <tableColumn id="6" name="AI Response (Summary)" dataDxfId="28"/>
+    <tableColumn id="7" name="Human Delta: Critical Thinking" dataDxfId="29"/>
+    <tableColumn id="8" name="Human Delta: Contextualization" dataDxfId="30"/>
+    <tableColumn id="9" name="Human Delta: Creative Synthesis" dataDxfId="31"/>
+    <tableColumn id="10" name="Human Delta: Decision Ownership" dataDxfId="32"/>
+    <tableColumn id="11" name="Evidence" dataDxfId="33"/>
+    <tableColumn id="12" name="Hallucination Detected?" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="AI_AuditLog_SWP_Template-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1466,90 +1790,102 @@
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="12" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="37.5" customHeight="1" spans="1:11">
-      <c r="A2" s="1">
+    <row r="2" ht="132" customHeight="1" spans="1:11">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="15" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" ht="22.5" customHeight="1"/>
-    <row r="4" ht="22.5" customHeight="1" spans="1:11">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
+    <row r="3" ht="22.5" customHeight="1" spans="1:11">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+    </row>
+    <row r="4" ht="44" customHeight="1" spans="1:11">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
     </row>
     <row r="5" ht="22.5" customHeight="1"/>
     <row r="6" ht="22.5" customHeight="1"/>
@@ -1565,7 +1901,7 @@
     <row r="16" ht="22.5" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" sqref="A4 A2:A3">
+    <dataValidation type="custom" allowBlank="1" sqref="A2:A4">
       <formula1>AND(ISNUMBER(A2),(NOT(OR(NOT(ISERROR(DATEVALUE(A2))),AND(ISNUMBER(A2),LEFT(CELL("format",A2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
@@ -1583,23 +1919,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="24.5555555555556" customWidth="1"/>
     <col min="2" max="2" width="24.4444444444444" customWidth="1"/>
     <col min="3" max="3" width="16.8888888888889" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="25.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="26.2222222222222" customWidth="1"/>
     <col min="6" max="6" width="24.8888888888889" customWidth="1"/>
     <col min="7" max="7" width="31" customWidth="1"/>
     <col min="8" max="8" width="28.2222222222222" customWidth="1"/>
     <col min="9" max="9" width="46.1111111111111" customWidth="1"/>
     <col min="10" max="10" width="30.5555555555556" customWidth="1"/>
     <col min="11" max="11" width="34.2222222222222" customWidth="1"/>
+    <col min="12" max="12" width="20.6666666666667" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1633,66 +1970,109 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1">
+    <row r="2" ht="264" spans="1:12">
+      <c r="A2" s="3">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>31</v>
       </c>
+      <c r="K2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="3" ht="31" customHeight="1"/>
-    <row r="4" spans="1:11">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
+    <row r="3" ht="129" customHeight="1" spans="1:12">
+      <c r="A3" s="6">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" sqref="A4 A2:A3">
+    <dataValidation type="custom" allowBlank="1" sqref="A2:A4">
       <formula1>AND(ISNUMBER(A2),(NOT(OR(NOT(ISERROR(DATEVALUE(A2))),AND(ISNUMBER(A2),LEFT(CELL("format",A2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId2" display="https://docs.google.com/spreadsheets/d/1F1ZIXU5moxQNmL9pzZxH1Xa7w1-iLA7heVZkgCAWiUE/edit?usp=sharing" tooltip="https://docs.google.com/spreadsheets/d/1F1ZIXU5moxQNmL9pzZxH1Xa7w1-iLA7heVZkgCAWiUE/edit?usp=sharing"/>
+    <hyperlink ref="K3" r:id="rId3" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1705,10 +2085,112 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2"/>
-  <sheetData/>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="3"/>
+  <cols>
+    <col min="2" max="2" width="12.2222222222222" customWidth="1"/>
+    <col min="3" max="3" width="16.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="15.5555555555556" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="23.1111111111111" customWidth="1"/>
+    <col min="7" max="7" width="28.1111111111111" customWidth="1"/>
+    <col min="8" max="8" width="37.2222222222222" customWidth="1"/>
+    <col min="9" max="9" width="26.8888888888889" customWidth="1"/>
+    <col min="10" max="10" width="37.4444444444444" customWidth="1"/>
+    <col min="11" max="11" width="55.3333333333333" customWidth="1"/>
+    <col min="12" max="12" width="84" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="52.8" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="2"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="6"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="2"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" sqref="A2:A4">
+      <formula1>AND(ISNUMBER(A2),(NOT(OR(NOT(ISERROR(DATEVALUE(A2))),AND(ISNUMBER(A2),LEFT(CELL("format",A2))="D")))))</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/AI_AuditLog_SWP_NguyenAnhMinh_DE190975.xlsx
+++ b/AI_AuditLog_SWP_NguyenAnhMinh_DE190975.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
   <si>
     <t>Entry #</t>
   </si>
@@ -164,6 +164,90 @@
   </si>
   <si>
     <t>Yes (Severe Hallucination &amp; Flawed Logic - AI tự bịa ra điểm số cao cho file trống và CV rác).</t>
+  </si>
+  <si>
+    <t>System Prompt Design &amp; Persona Adoption</t>
+  </si>
+  <si>
+    <t>Implementation (AI Core Engine - CV Scoring System)</t>
+  </si>
+  <si>
+    <t>AI mặc định thường đóng vai trò là một trợ lý thân thiện, dẫn đến việc nhận xét CV chung chung, sáo rỗng và thiếu tính thực chiến. Hệ thống cần một "nhân cách" khó tính, soi lỗi như một nhà tuyển dụng FAANG thực thụ.</t>
+  </si>
+  <si>
+    <t>"You are an elite Senior Technical Recruiter + ATS System + IT Career Mentor with 15+ years of experience... You are STRICT. You DO NOT give fake compliments... Return response in 12 detailed sections (Executive Summary, ATS Analysis, Technical Skills, etc.) with a 100-point scoring system."</t>
+  </si>
+  <si>
+    <t>AI đã nhập vai thành công (Persona adopted), loại bỏ hoàn toàn các câu khen ngợi thừa thãi. Kết quả trả về được định dạng cứng theo đúng 12 mục yêu cầu, chỉ ra trực diện các điểm yếu (Red flags) và tính toán điểm số chính xác theo thang 100 dựa trên 10 tiêu chí đã định nghĩa.</t>
+  </si>
+  <si>
+    <t>Tôi nhận định rằng giá trị cốt lõi của một hệ thống đánh giá CV không nằm ở những lời khen, mà ở việc chỉ ra chính xác điểm chết (Red flags). Tôi chủ động ép AI rũ bỏ sự "dĩ hòa vi quý" để trở nên "tàn nhẫn nhưng thực tế" (brutally honest).</t>
+  </si>
+  <si>
+    <t>Dựa trên thực tế tuyển dụng khốc liệt của ngành IT (FAANG standards, ATS screening), tôi cung cấp bối cảnh rõ ràng để AI hiểu nó đang đóng vai trò gác cổng (Gatekeeper) chứ không phải người tư vấn tâm lý.</t>
+  </si>
+  <si>
+    <t>Các CV ở Việt Nam thường chuộng form của TopCV (2 cột, dùng thanh bar kỹ năng). Tôi đưa 8 mẫu này vào bối cảnh để AI hiểu đặc thù trình bày của ứng viên nội địa, từ đó chấm điểm Layout thực tế hơn.</t>
+  </si>
+  <si>
+    <t>Ứng dụng kỹ thuật Multimodal (Đa phương thức - Kết hợp Text Prompt và Image Input) để thiết lập kỹ thuật Few-Shot Learning. Tôi nạp sẵn dữ liệu đầu vào (Input) đa dạng để "hiệu chỉnh" (Calibrate) lại mức độ khó dễ trong việc cho điểm của AI.</t>
+  </si>
+  <si>
+    <t>Yes (Đã kiểm soát được lỗi Hallucination ảo tưởng sức mạnh, cấm AI tự động sinh ra những lời khen không có căn cứ từ dữ liệu CV).</t>
+  </si>
+  <si>
+    <t>Contextual Constraints &amp; Branching Logic</t>
+  </si>
+  <si>
+    <t>Implementation (AI Core Engine - Ruleset Calibration)</t>
+  </si>
+  <si>
+    <t>Một CV của Frontend Developer không thể được đánh giá bằng cùng một thước đo với CV của DevOps hay AI/ML Engineer. AI cần có bộ luật phân tích (Ruleset) rẽ nhánh riêng biệt cho từng vị trí IT cụ thể.</t>
+  </si>
+  <si>
+    <t>"SPECIAL RULES FOR IT CVs: If role is Frontend focus on React ecosystem, state management, UI/UX... If role is Backend focus on API design, DB design, Scalability, Security... If DevOps evaluate CI/CD, Docker, Kubernetes, Cloud..."</t>
+  </si>
+  <si>
+    <t>AI đã nhận diện được các vị trí ứng tuyển khác nhau và kích hoạt đúng bộ tiêu chí chuyên sâu tương ứng. Ví dụ: Khi phân tích CV Backend, AI tập trung vào đánh giá kiến trúc Caching và API thay vì hỏi về Responsive Design.</t>
+  </si>
+  <si>
+    <t>Tôi phát hiện AI dễ bị đánh lừa bởi việc nhồi nhét từ khóa (Buzzword stuffing) nếu chỉ dùng một bộ lọc IT chung chung. Cần phải có ranh giới rõ ràng giữa các phân hệ (Front/Back/DevOps/AI).</t>
+  </si>
+  <si>
+    <t>Áp dụng kiến thức chuyên ngành Software Engineering thực tế để vạch ra các "điểm chạm" quan trọng nhất của từng vị trí (Ví dụ: DevOps thì phải nói đến Docker/K8s, Frontend thì phải rành State Management).</t>
+  </si>
+  <si>
+    <t>Tích hợp logic rẽ nhánh (If-Else) ngay trong bản thân Prompt. Kỹ thuật này biến một Prompt tĩnh thành một "Functions" linh hoạt, tự điều chỉnh thang đo dựa trên Role khai báo trong CV.</t>
+  </si>
+  <si>
+    <t>Yêu cầu AI phải đánh giá sâu vào kiến trúc (Architecture), bảo mật (Security), và khả năng mở rộng (Scalability) để phân biệt dự án làm theo Tutorial (cấp độ sinh viên) với dự án Production-level (cấp độ đi làm thật).</t>
+  </si>
+  <si>
+    <t>No (AI tuân thủ tuyệt đối các ràng buộc logic rẽ nhánh, không bị lẫn lộn tiêu chí giữa các Role).</t>
+  </si>
+  <si>
+    <t>Few-Shot Prompting &amp; Visual Data Processing</t>
+  </si>
+  <si>
+    <t>Testing &amp; Fine-Tuning (CV Layout &amp; ATS Parsing Performance)</t>
+  </si>
+  <si>
+    <t>AI cần hiểu được các format CV phức tạp phổ biến tại thị trường (đặc biệt là các template hai cột, chứa icon, biểu đồ) để kiểm tra khả năng đọc hiểu của hệ thống quét ATS, đồng thời tạo một "chuẩn đối sánh" (benchmark) về trình độ ứng viên.</t>
+  </si>
+  <si>
+    <t>"And at the same time, based on the following CVs that I will submit here, we can evaluate the criteria more accurately."</t>
+  </si>
+  <si>
+    <t>AI đã phân tích thành công bố cục (Layout) và bóc tách dữ liệu từ 8 bức ảnh CV. AI lưu trữ các mẫu này làm "Base knowledge" (Kiến thức nền) để hiểu rõ sự khác biệt về chất lượng nội dung giữa một CV xịn và một CV kém.</t>
+  </si>
+  <si>
+    <t>Tôi nhận định không thể chỉ Train AI bằng chữ (Text). Để đánh giá tiêu chí "ATS Compatibility" và "Resume Formatting", AI buộc phải được "nhìn" thấy các bản CV thực tế bị lỗi layout, nhồi nhét thông tin hoặc dùng sai font chữ.</t>
+  </si>
+  <si>
+    <t>Quyết định cung cấp hẳn 1 tập dữ liệu (Dataset) nhỏ gồm 8 CV để làm "chuẩn vàng" (Gold standard) thay vì để AI tự đoán mò tiêu chuẩn trình bày.</t>
+  </si>
+  <si>
+    <t>Yes (Lúc đầu AI có thể bị hoa mắt/đọc sai chữ do layout 2 cột phức tạp, nhưng nhờ nạp nhiều ảnh mẫu (Few-shot), AI đã học được cách quét text chính xác theo từng block).</t>
   </si>
 </sst>
 </file>
@@ -193,15 +277,23 @@
     </font>
     <font>
       <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
       <sz val="10"/>
       <color rgb="FF800080"/>
       <name val="Roboto"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -224,14 +316,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -694,28 +778,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -839,8 +923,32 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -848,18 +956,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -868,12 +970,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -883,7 +979,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1292,170 +1388,182 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
       <fill>
@@ -1499,7 +1607,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="AI_AuditLog_SWP_Template-style" pivot="0" count="4" xr9:uid="{3D066CE8-E913-42A9-9BED-7C92F5D4FDC9}">
+    <tableStyle name="AI_AuditLog_SWP_Template-style" pivot="0" count="4" xr9:uid="{47D42E33-6BA0-4088-B10B-2938AA1E8CDB}">
       <tableStyleElement type="wholeTable" dxfId="38"/>
       <tableStyleElement type="headerRow" dxfId="37"/>
       <tableStyleElement type="firstRowStripe" dxfId="36"/>
@@ -1790,102 +1898,102 @@
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:11">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" ht="132" customHeight="1" spans="1:11">
-      <c r="A2" s="13">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="19" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:11">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:11">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17" t="s">
+      <c r="A4" s="21"/>
+      <c r="B4" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
     </row>
     <row r="5" ht="22.5" customHeight="1"/>
     <row r="6" ht="22.5" customHeight="1"/>
@@ -1933,136 +2041,136 @@
     <col min="9" max="9" width="46.1111111111111" customWidth="1"/>
     <col min="10" max="10" width="30.5555555555556" customWidth="1"/>
     <col min="11" max="11" width="34.2222222222222" customWidth="1"/>
-    <col min="12" max="12" width="20.6666666666667" style="10" customWidth="1"/>
+    <col min="12" max="12" width="20.6666666666667" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" ht="264" spans="1:12">
-      <c r="A2" s="3">
+    <row r="2" ht="237.6" spans="1:12">
+      <c r="A2" s="4">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="10" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" ht="129" customHeight="1" spans="1:12">
-      <c r="A3" s="6">
+      <c r="A3" s="3">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="10" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="2"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2088,98 +2196,172 @@
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="3"/>
   <cols>
-    <col min="2" max="2" width="12.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="16.8888888888889" customWidth="1"/>
-    <col min="4" max="4" width="15.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="23.1111111111111" customWidth="1"/>
-    <col min="7" max="7" width="28.1111111111111" customWidth="1"/>
-    <col min="8" max="8" width="37.2222222222222" customWidth="1"/>
-    <col min="9" max="9" width="26.8888888888889" customWidth="1"/>
-    <col min="10" max="10" width="37.4444444444444" customWidth="1"/>
-    <col min="11" max="11" width="55.3333333333333" customWidth="1"/>
-    <col min="12" max="12" width="84" customWidth="1"/>
+    <col min="1" max="1" width="8.88888888888889" style="1"/>
+    <col min="2" max="2" width="12.2222222222222" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.8888888888889" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.1111111111111" style="1" customWidth="1"/>
+    <col min="7" max="7" width="28.1111111111111" style="1" customWidth="1"/>
+    <col min="8" max="8" width="37.2222222222222" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.8888888888889" style="1" customWidth="1"/>
+    <col min="10" max="10" width="37.4444444444444" style="1" customWidth="1"/>
+    <col min="11" max="11" width="55.3333333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="21.8888888888889" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="52.8" spans="1:12">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="26.4" spans="1:12">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="2"/>
+    <row r="2" ht="176" customHeight="1" spans="1:12">
+      <c r="A2" s="4">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="6"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="2"/>
+    <row r="3" ht="70" customHeight="1" spans="1:12">
+      <c r="A3" s="3">
+        <v>5</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>64</v>
+      </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="2"/>
+    <row r="4" ht="73" customHeight="1" spans="1:12">
+      <c r="A4" s="7">
+        <v>6</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>72</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2187,6 +2369,11 @@
       <formula1>AND(ISNUMBER(A2),(NOT(OR(NOT(ISERROR(DATEVALUE(A2))),AND(ISNUMBER(A2),LEFT(CELL("format",A2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+    <hyperlink ref="K3" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+    <hyperlink ref="K4" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <tableParts count="1">

--- a/AI_AuditLog_SWP_NguyenAnhMinh_DE190975.xlsx
+++ b/AI_AuditLog_SWP_NguyenAnhMinh_DE190975.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12240" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="2" r:id="rId2"/>
     <sheet name="Week 3" sheetId="3" r:id="rId3"/>
+    <sheet name="Week 4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="103">
   <si>
     <t>Entry #</t>
   </si>
@@ -248,6 +249,96 @@
   </si>
   <si>
     <t>Yes (Lúc đầu AI có thể bị hoa mắt/đọc sai chữ do layout 2 cột phức tạp, nhưng nhờ nạp nhiều ảnh mẫu (Few-shot), AI đã học được cách quét text chính xác theo từng block).</t>
+  </si>
+  <si>
+    <t>Content Generation &amp; System Persona Calibration</t>
+  </si>
+  <si>
+    <t>Implementation (Mentor Portal - Blog &amp; Content Management - `MentorPostBlog.jsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Khi Mentor tạo bài viết hướng dẫn trả lời phỏng vấn (Article), AI mặc định sinh nội dung rất lý thuyết, thiếu cấu trúc STAR (Situation, Task, Action, Result) và không chừa sẵn các thẻ phân loại (Category) cần thiết cho Frontend UI render.</t>
+  </si>
+  <si>
+    <t>"You are an experienced IT Interview Coach. Write a Markdown guide for software engineers on how to answer behavioral interview questions using the STAR framework. Include practical examples for Junior Web Developers. Format with clear headers and tags like category: interview-tips."</t>
+  </si>
+  <si>
+    <t>AI đóng vai chuyên gia hướng dẫn, tạo một khung sườn bài viết rất chuẩn về STAR framework có kèm ví dụ thực tế của một React Developer nhưng các đề mục bị chồng chéo. | Tôi nhận định bài viết hướng dẫn của Mentor cần phải tối giản hóa lý thuyết và tập trung vào các case study thực tế của lập trình viên Việt Nam. Không nên để AI tự định đoạt bố cục mà cần áp đặt sẵn khung mẫu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tôi nhận định bài viết hướng dẫn của Mentor cần phải tối giản hóa lý thuyết và tập trung vào các case study thực tế của lập trình viên Việt Nam. Không nên để AI tự định đoạt bố cục mà cần áp đặt sẵn khung mẫu. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đưa bài viết về bối cảnh phỏng vấn kỹ thuật thực tế tại các công ty CNTT Việt Nam (với các câu hỏi thường gặp như giải quyết conflict git hoặc sửa bug production gấp). </t>
+  </si>
+  <si>
+    <t>Thiết lập khung dữ liệu mẫu có trạng thái `isEditing` trong `MentorPostBlog.jsx` để tự động nạp bài viết STAR mẫu này vào ô textarea làm gợi ý sẵn cho Mentor.</t>
+  </si>
+  <si>
+    <t>Quyết định sử dụng Markdown nguyên bản thay vì các trình soạn thảo WYSIWYG phức tạp để Mentor dễ dàng copy-paste code snippets và định dạng nhanh chóng.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> No (AI tuân thủ tuyệt đối cấu trúc STAR yêu cầu và định dạng Markdown chuẩn).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component Logic &amp; Dynamic Styling Calibration </t>
+  </si>
+  <si>
+    <t>Implementation (Mentor Portal - Video Assessment Scoring - `MentorReviewDetail.jsx`)</t>
+  </si>
+  <si>
+    <t>Thanh trượt điểm số (Scoring Sliders) cho 3 tiêu chí: Technical, Communication và Problem Solving bị mất đồng bộ màu nền của dải tiến độ (progress bar) khi Mentor kéo chọn từ 0 đến 10.</t>
+  </si>
+  <si>
+    <t>"Write a React state handler and dynamic inline style calculation for input range elements so that the background gradient fills dynamically from left to right based on the selected value (0 to 10), using custom colors like var(--color-moss) and var(--color-accent)."</t>
+  </si>
+  <si>
+    <t>AI cung cấp hàm xử lý sự kiện `handleScoreChange` và công thức tính phần trăm nền `linear-gradient` dựa trên điểm số nhân với 10.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tôi phát hiện nếu chỉ dùng sự kiện `onChange` thông thường thì trên một số trình duyệt cũ, dải tiến độ sẽ không cập nhật tức thì. Cần ép kiểu số nguyên (`parseInt`) để tránh lỗi truyền dữ liệu dạng chuỗi. </t>
+  </si>
+  <si>
+    <t>Đồng bộ dải màu tiến độ với hệ thống nhận diện thương hiệu "ITA Earthy System" (Moss cho giao tiếp, Accent cho kỹ thuật, Earth cho giải quyết vấn đề).</t>
+  </si>
+  <si>
+    <t>Kết hợp trực tiếp thuộc tính CSS `appearance: none` và inline `background` gradient lồng ghép biến trạng thái React (`feedback[key]`) để tạo ra hiệu ứng chuyển động mượt mà không cần thư viện bên thứ ba.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Giới hạn thang điểm từ 0-10 thay vì 0-100 để đơn giản hóa quá trình chấm điểm thủ công của Mentor và giữ giao diện sạch sẽ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No (AI viết đúng giải pháp tính toán inline style động). </t>
+  </si>
+  <si>
+    <t>Integration &amp; Error Boundary Resolution</t>
+  </si>
+  <si>
+    <t>Integration (CV Upload &amp; AI Assessment Pipeline - `cvStorageService.js`)</t>
+  </si>
+  <si>
+    <t>Khi kết nối luồng tải CV lên của Candidate với Supabase Storage, API liên tục trả về lỗi 'Payload Too Large' hoặc lỗi phân quyền RLS khi người dùng chưa đăng nhập (Guest) tải tệp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "How to resolve Supabase Storage RLS policy errors for anonymous guest uploads in a React application? Provide a storage client wrapper that skips metadata DB inserts if the user is a guest, uploading files only to a public folder."</t>
+  </si>
+  <si>
+    <t>AI đề xuất cấu hình chính sách RLS cho phép anonymous access và viết mã hàm kiểm tra điều kiện session trước khi thực hiện câu lệnh ghi thông tin.</t>
+  </si>
+  <si>
+    <t>Tôi thấy đề xuất của AI chưa bảo mật vì mở quyền public quá rộng. Giải pháp an toàn hơn là mã hóa tên tệp bằng timestamp + hash ngẫu nhiên trước khi lưu vào thư mục `guest/` để tránh người dùng khách đọc trộm tệp của nhau.</t>
+  </si>
+  <si>
+    <t>Thiết lập kích thước tệp tối đa 10MB trong code client trước khi gọi API để tránh làm quá tải băng thông của Supabase free tier.</t>
+  </si>
+  <si>
+    <t>Tích hợp cơ chế tự động dọn dẹp (auto-cleanup schedule) trên Supabase hoặc xử lý xóa file tạm ở phía client để tối ưu hóa bộ nhớ lưu trữ.</t>
+  </si>
+  <si>
+    <t>Quyết định viết một service trung gian `cvStorageService.js` đóng gói toàn bộ logic upload để các component khác có thể tái sử dụng dễ dàng mà không bị phụ thuộc vào cấu hình Supabase SDK.</t>
+  </si>
+  <si>
+    <t>Yes (AI từng đề xuất sử dụng hàm `supabase.storage.from().upload()` với tham số cấu hình sai phiên bản API gây lỗi runtime, tôi đã đọc tài liệu Supabase và sửa lại thủ công). |</t>
   </si>
 </sst>
 </file>
@@ -291,18 +382,18 @@
     </font>
     <font>
       <u/>
-      <sz val="10"/>
-      <color rgb="FF800080"/>
-      <name val="Roboto"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF800080"/>
+      <name val="Roboto"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -796,7 +887,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -923,27 +1014,30 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -958,10 +1052,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1040,7 +1134,7 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="51">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -1564,6 +1658,174 @@
         <color rgb="FF000000"/>
       </font>
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -1607,11 +1869,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="AI_AuditLog_SWP_Template-style" pivot="0" count="4" xr9:uid="{47D42E33-6BA0-4088-B10B-2938AA1E8CDB}">
-      <tableStyleElement type="wholeTable" dxfId="38"/>
-      <tableStyleElement type="headerRow" dxfId="37"/>
-      <tableStyleElement type="firstRowStripe" dxfId="36"/>
-      <tableStyleElement type="secondRowStripe" dxfId="35"/>
+    <tableStyle name="AI_AuditLog_SWP_Template-style" pivot="0" count="4" xr9:uid="{FE0E324C-2B17-4CE7-9274-230385336E75}">
+      <tableStyleElement type="wholeTable" dxfId="50"/>
+      <tableStyleElement type="headerRow" dxfId="49"/>
+      <tableStyleElement type="firstRowStripe" dxfId="48"/>
+      <tableStyleElement type="secondRowStripe" dxfId="47"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1676,6 +1938,26 @@
     <tableColumn id="10" name="Human Delta: Decision Ownership" dataDxfId="32"/>
     <tableColumn id="11" name="Evidence" dataDxfId="33"/>
     <tableColumn id="12" name="Hallucination Detected?" dataDxfId="34"/>
+  </tableColumns>
+  <tableStyleInfo name="AI_AuditLog_SWP_Template-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SWP_345" displayName="SWP_345" ref="A1:L4">
+  <tableColumns count="12">
+    <tableColumn id="1" name="Entry #" dataDxfId="35"/>
+    <tableColumn id="2" name="Prompt Type" dataDxfId="36"/>
+    <tableColumn id="3" name="Stage/Component" dataDxfId="37"/>
+    <tableColumn id="4" name="Problem/Context" dataDxfId="38"/>
+    <tableColumn id="5" name="Prompt to AI" dataDxfId="39"/>
+    <tableColumn id="6" name="AI Response (Summary)" dataDxfId="40"/>
+    <tableColumn id="7" name="Human Delta: Critical Thinking" dataDxfId="41"/>
+    <tableColumn id="8" name="Human Delta: Contextualization" dataDxfId="42"/>
+    <tableColumn id="9" name="Human Delta: Creative Synthesis" dataDxfId="43"/>
+    <tableColumn id="10" name="Human Delta: Decision Ownership" dataDxfId="44"/>
+    <tableColumn id="11" name="Evidence" dataDxfId="45"/>
+    <tableColumn id="12" name="Hallucination Detected?" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="AI_AuditLog_SWP_Template-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1898,102 +2180,102 @@
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:11">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" ht="132" customHeight="1" spans="1:11">
-      <c r="A2" s="17">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="20" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:11">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
+      <c r="A3" s="21"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:11">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="22"/>
+      <c r="B4" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="21"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
     </row>
     <row r="5" ht="22.5" customHeight="1"/>
     <row r="6" ht="22.5" customHeight="1"/>
@@ -2041,136 +2323,136 @@
     <col min="9" max="9" width="46.1111111111111" customWidth="1"/>
     <col min="10" max="10" width="30.5555555555556" customWidth="1"/>
     <col min="11" max="11" width="34.2222222222222" customWidth="1"/>
-    <col min="12" max="12" width="20.6666666666667" style="8" customWidth="1"/>
+    <col min="12" max="12" width="20.6666666666667" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="11" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" ht="237.6" spans="1:12">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>2</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="11" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" ht="129" customHeight="1" spans="1:12">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>3</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="11" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="10"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2196,171 +2478,362 @@
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="12.2222222222222" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.8888888888889" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5555555555556" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23.1111111111111" style="1" customWidth="1"/>
-    <col min="7" max="7" width="28.1111111111111" style="1" customWidth="1"/>
-    <col min="8" max="8" width="37.2222222222222" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.8888888888889" style="1" customWidth="1"/>
-    <col min="10" max="10" width="37.4444444444444" style="1" customWidth="1"/>
-    <col min="11" max="11" width="55.3333333333333" style="1" customWidth="1"/>
-    <col min="12" max="12" width="21.8888888888889" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.88888888888889" style="7"/>
+    <col min="2" max="2" width="12.2222222222222" style="7" customWidth="1"/>
+    <col min="3" max="3" width="16.8888888888889" style="7" customWidth="1"/>
+    <col min="4" max="4" width="15.5555555555556" style="7" customWidth="1"/>
+    <col min="5" max="5" width="18" style="7" customWidth="1"/>
+    <col min="6" max="6" width="23.1111111111111" style="7" customWidth="1"/>
+    <col min="7" max="7" width="28.1111111111111" style="7" customWidth="1"/>
+    <col min="8" max="8" width="37.2222222222222" style="7" customWidth="1"/>
+    <col min="9" max="9" width="26.8888888888889" style="7" customWidth="1"/>
+    <col min="10" max="10" width="37.4444444444444" style="7" customWidth="1"/>
+    <col min="11" max="11" width="55.3333333333333" style="7" customWidth="1"/>
+    <col min="12" max="12" width="21.8888888888889" style="7" customWidth="1"/>
+    <col min="13" max="16384" width="8.88888888888889" style="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.4" spans="1:12">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" ht="176" customHeight="1" spans="1:12">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="3" ht="70" customHeight="1" spans="1:12">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="4" ht="73" customHeight="1" spans="1:12">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" sqref="A2:A4">
+      <formula1>AND(ISNUMBER(A2),(NOT(OR(NOT(ISERROR(DATEVALUE(A2))),AND(ISNUMBER(A2),LEFT(CELL("format",A2))="D")))))</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+    <hyperlink ref="K3" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+    <hyperlink ref="K4" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="1" width="18.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="17.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="19.1111111111111" customWidth="1"/>
+    <col min="4" max="4" width="24.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="26.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="25.5555555555556" customWidth="1"/>
+    <col min="7" max="7" width="26.4444444444444" customWidth="1"/>
+    <col min="8" max="8" width="35.4444444444444" customWidth="1"/>
+    <col min="9" max="9" width="29.7777777777778" customWidth="1"/>
+    <col min="10" max="10" width="37.6666666666667" customWidth="1"/>
+    <col min="11" max="11" width="42.6666666666667" customWidth="1"/>
+    <col min="12" max="12" width="65.3333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" ht="106" customHeight="1" spans="1:12">
+      <c r="A2" s="3">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" ht="123" customHeight="1" spans="1:12">
+      <c r="A3" s="2">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" ht="65" customHeight="1" spans="1:12">
+      <c r="A4" s="6">
+        <v>9</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/AI_AuditLog_SWP_NguyenAnhMinh_DE190975.xlsx
+++ b/AI_AuditLog_SWP_NguyenAnhMinh_DE190975.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="12240" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
     <sheet name="Week 2" sheetId="2" r:id="rId2"/>
     <sheet name="Week 3" sheetId="3" r:id="rId3"/>
     <sheet name="Week 4" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 5" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="133">
   <si>
     <t>Entry #</t>
   </si>
@@ -339,6 +340,96 @@
   </si>
   <si>
     <t>Yes (AI từng đề xuất sử dụng hàm `supabase.storage.from().upload()` với tham số cấu hình sai phiên bản API gây lỗi runtime, tôi đã đọc tài liệu Supabase và sửa lại thủ công). |</t>
+  </si>
+  <si>
+    <t>Test Automation &amp; Cypress Scripting</t>
+  </si>
+  <si>
+    <t>Testing (Mentor Portal - Blog Creation E2E - `mentor_blog.cy.js`</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cần viết kịch bản Cypress giả lập luồng tạo bài viết blog của Mentor để test tự động, nhưng cú pháp thao tác với DOM và Markdown editor bị timeout hoặc lỗi không tìm thấy phần tử.</t>
+  </si>
+  <si>
+    <t>"Write a Cypress E2E test script to simulate a user filling out the Mentor Blog form (title, category, content) and clicking the 'Save Draft' button. Handle the asynchronous rendering of the markdown preview."</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AI cung cấp script cơ bản sử dụng `cy.get()` và `.type()`, nhưng thiếu lệnh chờ cần thiết để iframe của markdown editor load xong.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhận ra nếu mạng chậm, test sẽ fail ngẫu nhiên (flaky test). Cần thêm cơ chế intercept API thay vì dùng wait() cứng do AI cung cấp. </t>
+  </si>
+  <si>
+    <t>Điều chỉnh script áp dụng riêng cho môi trường localhost của đồ án với các CSS classes chuẩn của giao diện dự án ITA.</t>
+  </si>
+  <si>
+    <t>Sử dụng `cy.intercept()` để bắt request upload ảnh trong markdown và mock dữ liệu trả về để test chạy ổn định và nhanh hơn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quyết định viết riêng một custom Cypress command `cy.fillBlogForm()` để dễ dàng tái sử dụng trong các bộ test case khác. </t>
+  </si>
+  <si>
+    <t>No (AI sinh mã Cypress chuẩn nhưng chưa xử lý tốt tình huống bất đồng bộ phức tạp).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Performance Optimization &amp; React Hooks</t>
+  </si>
+  <si>
+    <t>Implementation (Mentor Portal - Mentor Schedule - `MentorSchedule.jsx`</t>
+  </si>
+  <si>
+    <t>Khi Mentor kéo thả chuột để chọn lịch rảnh (availability) trên giao diện lịch tuần, ứng dụng bị giật lag (re-render nhiều lần) do state quản lý mảng thời gian quá lớn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "How to optimize a React weekly calendar component where drag-and-drop cell selection causes heavy re-renders? Should I use useMemo or switch to a local state reference?"</t>
+  </si>
+  <si>
+    <t>AI khuyên nên bọc component lịch bằng `React.memo` và dùng `useCallback` cho hàm `handleDrag`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gợi ý của AI đúng nhưng chưa giải quyết triệt để. Việc cập nhật mảng state lớn ở mỗi sự kiện `onMouseMove` là nguyên nhân chính. Cần chuyển sang dùng `useRef`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tối ưu hóa hành vi kéo thả cho phù hợp với logic đặt lịch phỏng vấn (block 30 phút/slot) của ứng dụng. </t>
+  </si>
+  <si>
+    <t>Kết hợp `useRef` để lưu trữ tiến trình kéo chuột tạm thời và sử dụng DOM manipulation thuần để thêm CSS class `selected` giúp giao diện mượt mà, sau đó mới cập nhật React state ở sự kiện `onMouseUp`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Từ chối sử dụng thư viện quản lý state phức tạp, giữ logic ở nội bộ component để ứng dụng nhẹ nhất có thể. </t>
+  </si>
+  <si>
+    <t>Yes (AI gợi ý dùng useMemo sai cách khiến ứng dụng đôi khi không hiển thị đúng vùng chọn).</t>
+  </si>
+  <si>
+    <t>Data Modeling &amp; Boundary Value Testing</t>
+  </si>
+  <si>
+    <t>Quality Assurance (CV Upload Pipeline - `CVManager.jsx`</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cần xác định tập dữ liệu kiểm thử (Test Data) cho chức năng kéo thả CV, đảm bảo bao phủ các trường hợp biên (Boundary Value) của dung lượng file (chính xác 10MB).</t>
+  </si>
+  <si>
+    <t>"Generate a list of boundary value test cases for a file upload component with a strict 5MB limit. Include exact file sizes in bytes that I should test."</t>
+  </si>
+  <si>
+    <t>AI liệt kê các test case với dung lượng 7.99MB, 9.00MB, và 8.01MB, tính ra chính xác số byte (ví dụ: 5242880 bytes).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dữ liệu AI tính toán rất chuẩn xác, giúp  thiết lập các mock file trong Jest dễ dàng. Tuy nhiên AI bỏ quên bài toán định dạng MIME type bị giả mạo. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bổ sung thêm test case cho trường hợp Candidate cố tình đổi đuôi file `.exe` thành `.pdf` rồi upload lên hệ thống. </t>
+  </si>
+  <si>
+    <t>Tạo một script nhỏ bằng Node.js để sinh ra các file rác có dung lượng chính xác tới từng byte để test thay vì tìm kiếm file mẫu trên mạng.</t>
+  </si>
+  <si>
+    <t>Quyết định áp dụng kiểm tra chữ ký file (magic numbers header) ở frontend kết hợp backend để chặn triệt để file độc hại, không chỉ dựa vào tên đuôi mở rộng.</t>
+  </si>
+  <si>
+    <t>No (Dữ liệu số liệu do AI tính toán là hoàn toàn chính xác).</t>
   </si>
 </sst>
 </file>
@@ -1014,8 +1105,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1134,7 +1228,7 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="51">
+  <dxfs count="63">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -1662,170 +1756,350 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+      <alignment vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
       <fill>
@@ -1869,11 +2143,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="AI_AuditLog_SWP_Template-style" pivot="0" count="4" xr9:uid="{FE0E324C-2B17-4CE7-9274-230385336E75}">
-      <tableStyleElement type="wholeTable" dxfId="50"/>
-      <tableStyleElement type="headerRow" dxfId="49"/>
-      <tableStyleElement type="firstRowStripe" dxfId="48"/>
-      <tableStyleElement type="secondRowStripe" dxfId="47"/>
+    <tableStyle name="AI_AuditLog_SWP_Template-style" pivot="0" count="4" xr9:uid="{5A62E572-F47F-4A74-81DC-34D29D03984A}">
+      <tableStyleElement type="wholeTable" dxfId="62"/>
+      <tableStyleElement type="headerRow" dxfId="61"/>
+      <tableStyleElement type="firstRowStripe" dxfId="60"/>
+      <tableStyleElement type="secondRowStripe" dxfId="59"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1958,6 +2232,26 @@
     <tableColumn id="10" name="Human Delta: Decision Ownership" dataDxfId="44"/>
     <tableColumn id="11" name="Evidence" dataDxfId="45"/>
     <tableColumn id="12" name="Hallucination Detected?" dataDxfId="46"/>
+  </tableColumns>
+  <tableStyleInfo name="AI_AuditLog_SWP_Template-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="SWP_3456" displayName="SWP_3456" ref="A1:L4">
+  <tableColumns count="12">
+    <tableColumn id="1" name="Entry #" dataDxfId="47"/>
+    <tableColumn id="2" name="Prompt Type" dataDxfId="48"/>
+    <tableColumn id="3" name="Stage/Component" dataDxfId="49"/>
+    <tableColumn id="4" name="Problem/Context" dataDxfId="50"/>
+    <tableColumn id="5" name="Prompt to AI" dataDxfId="51"/>
+    <tableColumn id="6" name="AI Response (Summary)" dataDxfId="52"/>
+    <tableColumn id="7" name="Human Delta: Critical Thinking" dataDxfId="53"/>
+    <tableColumn id="8" name="Human Delta: Contextualization" dataDxfId="54"/>
+    <tableColumn id="9" name="Human Delta: Creative Synthesis" dataDxfId="55"/>
+    <tableColumn id="10" name="Human Delta: Decision Ownership" dataDxfId="56"/>
+    <tableColumn id="11" name="Evidence" dataDxfId="57"/>
+    <tableColumn id="12" name="Hallucination Detected?" dataDxfId="58"/>
   </tableColumns>
   <tableStyleInfo name="AI_AuditLog_SWP_Template-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2180,102 +2474,102 @@
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:11">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="18" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" ht="132" customHeight="1" spans="1:11">
-      <c r="A2" s="18">
+      <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:11">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:11">
-      <c r="A4" s="22"/>
-      <c r="B4" s="22" t="s">
+      <c r="A4" s="23"/>
+      <c r="B4" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
     </row>
     <row r="5" ht="22.5" customHeight="1"/>
     <row r="6" ht="22.5" customHeight="1"/>
@@ -2323,136 +2617,136 @@
     <col min="9" max="9" width="46.1111111111111" customWidth="1"/>
     <col min="10" max="10" width="30.5555555555556" customWidth="1"/>
     <col min="11" max="11" width="34.2222222222222" customWidth="1"/>
-    <col min="12" max="12" width="20.6666666666667" style="9" customWidth="1"/>
+    <col min="12" max="12" width="20.6666666666667" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" ht="237.6" spans="1:12">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>2</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="12" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" ht="129" customHeight="1" spans="1:12">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>3</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="12" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="11"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="12"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2478,170 +2772,170 @@
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="7"/>
-    <col min="2" max="2" width="12.2222222222222" style="7" customWidth="1"/>
-    <col min="3" max="3" width="16.8888888888889" style="7" customWidth="1"/>
-    <col min="4" max="4" width="15.5555555555556" style="7" customWidth="1"/>
-    <col min="5" max="5" width="18" style="7" customWidth="1"/>
-    <col min="6" max="6" width="23.1111111111111" style="7" customWidth="1"/>
-    <col min="7" max="7" width="28.1111111111111" style="7" customWidth="1"/>
-    <col min="8" max="8" width="37.2222222222222" style="7" customWidth="1"/>
-    <col min="9" max="9" width="26.8888888888889" style="7" customWidth="1"/>
-    <col min="10" max="10" width="37.4444444444444" style="7" customWidth="1"/>
-    <col min="11" max="11" width="55.3333333333333" style="7" customWidth="1"/>
-    <col min="12" max="12" width="21.8888888888889" style="7" customWidth="1"/>
-    <col min="13" max="16384" width="8.88888888888889" style="7"/>
+    <col min="1" max="1" width="8.88888888888889" style="8"/>
+    <col min="2" max="2" width="12.2222222222222" style="8" customWidth="1"/>
+    <col min="3" max="3" width="16.8888888888889" style="8" customWidth="1"/>
+    <col min="4" max="4" width="15.5555555555556" style="8" customWidth="1"/>
+    <col min="5" max="5" width="18" style="8" customWidth="1"/>
+    <col min="6" max="6" width="23.1111111111111" style="8" customWidth="1"/>
+    <col min="7" max="7" width="28.1111111111111" style="8" customWidth="1"/>
+    <col min="8" max="8" width="37.2222222222222" style="8" customWidth="1"/>
+    <col min="9" max="9" width="26.8888888888889" style="8" customWidth="1"/>
+    <col min="10" max="10" width="37.4444444444444" style="8" customWidth="1"/>
+    <col min="11" max="11" width="55.3333333333333" style="8" customWidth="1"/>
+    <col min="12" max="12" width="21.8888888888889" style="8" customWidth="1"/>
+    <col min="13" max="16384" width="8.88888888888889" style="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.4" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" ht="176" customHeight="1" spans="1:12">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="3" ht="70" customHeight="1" spans="1:12">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="4" ht="73" customHeight="1" spans="1:12">
-      <c r="A4" s="6">
+      <c r="A4" s="7">
         <v>6</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="3" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2685,155 +2979,347 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" ht="106" customHeight="1" spans="1:12">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="3" ht="123" customHeight="1" spans="1:12">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="4" ht="65" customHeight="1" spans="1:12">
-      <c r="A4" s="6">
+      <c r="A4" s="7">
         <v>9</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="3" t="s">
         <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" sqref="A2:A4">
+      <formula1>AND(ISNUMBER(A2),(NOT(OR(NOT(ISERROR(DATEVALUE(A2))),AND(ISNUMBER(A2),LEFT(CELL("format",A2))="D")))))</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+    <hyperlink ref="K3" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+    <hyperlink ref="K4" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="3"/>
+  <cols>
+    <col min="1" max="1" width="8.88888888888889" style="1"/>
+    <col min="2" max="2" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7777777777778" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.4444444444444" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.6666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="28.6666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="29.3333333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24.4444444444444" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.5555555555556" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24.8888888888889" style="1" customWidth="1"/>
+    <col min="12" max="12" width="35.1111111111111" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88888888888889" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26.4" spans="1:12">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" ht="87" customHeight="1" spans="1:12">
+      <c r="A2" s="4">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" ht="79" customHeight="1" spans="1:12">
+      <c r="A3" s="3">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" ht="99" customHeight="1" spans="1:12">
+      <c r="A4" s="7">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/AI_AuditLog_SWP_NguyenAnhMinh_DE190975.xlsx
+++ b/AI_AuditLog_SWP_NguyenAnhMinh_DE190975.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12240" activeTab="4"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="Week 3" sheetId="3" r:id="rId3"/>
     <sheet name="Week 4" sheetId="4" r:id="rId4"/>
     <sheet name="Week 5" sheetId="5" r:id="rId5"/>
+    <sheet name="Week 6" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="193">
   <si>
     <t>Entry #</t>
   </si>
@@ -430,6 +431,186 @@
   </si>
   <si>
     <t>No (Dữ liệu số liệu do AI tính toán là hoàn toàn chính xác).</t>
+  </si>
+  <si>
+    <t>System Design &amp; Use Case Modeling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requirement Analysis (Mentor Sub-system - Booking Flow) </t>
+  </si>
+  <si>
+    <t>Gặp khó khăn khi xác định các luồng nghiệp vụ (flows) cho chức năng đặt lịch phỏng vấn giữa Candidate và Mentor. Không rõ khi nào dùng &lt;&lt;include&gt;&gt; hay &lt;&lt;extend&gt;&gt; cho các hành động chấp nhận/từ chối lịch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "Based on standard UML rules, how should I model a 'Process Booking Requests' use case for a Mentor? The mentor needs to view schedule availability, and then can either accept or decline the request."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI giải thích chuẩn UML: 'View Schedule Availability' là bắt buộc nên dùng &lt;&lt;include&gt;&gt;, còn 'Accept' và 'Decline' là các luồng tùy chọn nên dùng &lt;&lt;extend&gt;&gt;. </t>
+  </si>
+  <si>
+    <t>Gợi ý của AI hoàn toàn hợp lý về mặt lý thuyết UML. Mình áp dụng trực tiếp cấu trúc này vào bản vẽ Use Case Diagram của dự án ITA.</t>
+  </si>
+  <si>
+    <t>Điều chỉnh tên gọi cho sát với thực tế dự án: "Process Booking Requests" thay vì tên chung chung, đảm bảo khớp với các module React.</t>
+  </si>
+  <si>
+    <t>Vẽ lại biểu đồ Use Case hoàn chỉnh trên công cụ thiết kế, kết nối Actor Mentor với các nhánh extend/include chuẩn xác theo tư vấn của AI.</t>
+  </si>
+  <si>
+    <t>Quyết định gom luồng Accept/Decline thành nhánh extend của một Use Case lớn để giảm số lượng Use Case rác trong tài liệu phân tích thiết kế.</t>
+  </si>
+  <si>
+    <t>No (AI tư vấn đúng quy tắc UML quốc tế).</t>
+  </si>
+  <si>
+    <t>UML Refactoring &amp; Relationship Mapping</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Requirement Analysis (Mentor Sub-system - Blog Management)</t>
+  </si>
+  <si>
+    <t>Cần chuẩn hóa lại sơ đồ Use Case cho tính năng quản lý bài viết của Mentor (Public Mentor Blogs) để phân tách rõ hành vi tạo mới và cập nhật bài viết.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"In a Use Case diagram, if a Mentor has a primary action 'Public Mentor Blogs', how do I represent the actions 'Create Blogs' and 'Update Blogs'? Are they &lt;&lt;extend&gt;&gt; or generalized?" </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AI khuyên nên sử dụng &lt;&lt;extend&gt;&gt; từ 'Public Mentor Blogs' trỏ tới 'Create Blogs' và 'Update Blogs' vì đây là các hành động mở rộng từ việc quản lý chung.</t>
+  </si>
+  <si>
+    <t>Nhận ra AI có sự nhầm lẫn nhẹ về chiều mũi tên của &lt;&lt;extend&gt;&gt; trong chuẩn UML (mũi tên phải hướng từ Use Case mở rộng về Use Case gốc).</t>
+  </si>
+  <si>
+    <t>Đảm bảo luồng 'Public Mentor Blogs' được xem là Base Use Case chứa logic hiển thị danh sách, còn Create/Update là các tính năng phát sinh.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chỉnh sửa lại chiều mũi tên đứt nét (dashed arrow) trong bản vẽ để mũi tên &lt;&lt;extend&gt;&gt; từ 'Create Blogs' trỏ ngược về 'Public Mentor Blogs'.</t>
+  </si>
+  <si>
+    <t>Kiên quyết tuân thủ quy tắc UML quốc tế thay vì vẽ theo chiều mũi tên thuận miệng thông thường mà AI từng gợi ý.</t>
+  </si>
+  <si>
+    <t>Yes (AI nhầm lẫn chiều mũi tên đứt nét của quan hệ &lt;&lt;extend&gt;&gt; trong văn bản giải thích).</t>
+  </si>
+  <si>
+    <t>Feature Decomposition &amp; Naming Convention</t>
+  </si>
+  <si>
+    <t>Requirement Analysis (Mentor Sub-system - Video Review)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đang băn khoăn về cách cấu trúc chức năng đánh giá ứng viên. Việc xem video và gửi feedback (chấm điểm) nên là 2 Use Case độc lập hay gộp chung? </t>
+  </si>
+  <si>
+    <t>"For an interview platform, a Mentor reviews a candidate's video and must submit a score/feedback. Should 'Submit Video Feedback &amp; Score' be a separate Use Case with an &lt;&lt;include&gt;&gt; relationship from 'Review Candidate Video'?"</t>
+  </si>
+  <si>
+    <t>AI phân tích: Vì việc gửi điểm là hành động bắt buộc (mandatory part) của quá trình review, nên tách ra thành một Use Case riêng và dùng quan hệ &lt;&lt;include&gt;&gt;.</t>
+  </si>
+  <si>
+    <t>Đồng tình với AI vì việc tách Use Case giúp việc viết đặc tả (Use Case Specification) và thiết kế màn hình giao diện 'MentorReviewDetail' rõ ràng hơn.</t>
+  </si>
+  <si>
+    <t>Tự động phát hiện và sửa lại lỗi chính tả (AI sinh ra chữ 'Summit' thay vì 'Submit') để đưa vào bản vẽ Draw.io chính thức.</t>
+  </si>
+  <si>
+    <t>Lấy cấu trúc Use Case này làm nền tảng cốt lõi để code UI màn hình 'MentorReviewDetail.jsx' chia làm 2 phần: Video Player và Feedback Form.</t>
+  </si>
+  <si>
+    <t>Quyết định nhóm chức năng 'Contact Candidate' thành một Use Case độc lập riêng biệt không dính líu đến luồng review video.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes (AI sinh ra lỗi chính tả 'Summit Video Feedback' thay vì 'Submit'). </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Feature Implementation &amp; Business Logic</t>
+  </si>
+  <si>
+    <t>Implementation (Candidate Portal - Mentor Booking - `BookMentor.jsx`)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cần giới hạn số lượt đặt lịch của Candidate (Quota limit) dựa trên gói cước (Free: 0, Pro: 1, Premium: 5) trong vòng 30 ngày để đảm bảo mô hình kinh doanh </t>
+  </si>
+  <si>
+    <t xml:space="preserve">"How to implement a quota system in React and Supabase where 'Free' users cannot book mentors, 'Pro' users can book 1 session, and 'Premium' users can book 5 sessions per 30-day rolling cycle?" </t>
+  </si>
+  <si>
+    <t>AI gợi ý viết hàm kiểm tra tổng số bản ghi từ bảng `mentor_bookings` bằng lệnh count gte `created_at` trong 30 ngày qua và so sánh với limit cứng.</t>
+  </si>
+  <si>
+    <t>Nhận thấy việc chỉ khóa UI là chưa đủ bảo mật, hacker có thể bypass. Tuy nhiên, ở góc độ frontend, tôi thiết kế trước UI hiển thị rõ số lượt đã dùng/tổng số lượt (`used/limit`) và nút Upgrade.</t>
+  </si>
+  <si>
+    <t>Gộp logic tính Quota (`fetchMentorAndQuota`) ngay trong lúc tải thông tin Mentor để tối ưu giảm số lượng Network request.</t>
+  </si>
+  <si>
+    <t>Phối hợp thẻ cảnh báo `AlertCircle` / `CheckCircle2` với 3 mã màu (Đỏ/Cam/Xanh) phản ánh trực quan 3 trạng thái: Hết hạn mức, Đã dùng 1 phần, và Còn trống.</t>
+  </si>
+  <si>
+    <t>Chặn cứng quyền thao tác của gói Free, hiển thị box màu đỏ yêu cầu nâng cấp thay vì giấu đi nút Đặt lịch, giúp thúc đẩy tỷ lệ chuyển đổi (conversion rate).</t>
+  </si>
+  <si>
+    <t>No (AI đưa ra query lọc `.gte('created_at', thirtyDaysAgo)` cực kỳ chuẩn xác).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Fetching &amp; Conflict Resolution </t>
+  </si>
+  <si>
+    <t>Implementation (Mentor Booking - Schedule Availability - `BookMentor.jsx`)</t>
+  </si>
+  <si>
+    <t>Khi một khung giờ đã được ứng viên khác đặt trước, nó cần phải bị vô hiệu hóa (disabled) trong dropdown chọn giờ để tránh double-booking (đặt trùng lịch).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Write a React useEffect to fetch existing bookings from Supabase based on a selected date, and disable those specific time slots in an HTML select dropdown." </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI cung cấp code fetch dữ liệu theo `booking_date` và dùng hàm `.includes()` để map qua mảng option, set thuộc tính `disabled` cho các option đã có người đặt. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tự phát hiện lỗ hổng logic: AI quên tính tới trường hợp lịch đã bị Mentor từ chối (`rejected`). Nếu bị từ chối thì khung giờ đó phải được giải phóng. </t>
+  </si>
+  <si>
+    <t>Bổ sung thêm điều kiện truy vấn `.neq('status', 'rejected')` vào Supabase filter để giải phóng chính xác các khung giờ trống cho người đến sau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Thêm hậu tố chuỗi "(Đã có người đặt)" trực tiếp vào nhãn `option` bị vô hiệu hóa trên giao diện để người dùng hiểu lý do vì sao không chọn được.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không dùng các thư viện Datepicker phức tạp, mà sử dụng mảng Array cố định (08:00 - 09:00,...) kết hợp thẻ `&lt;select&gt;` chuẩn để tối ưu hiệu năng. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes (AI quên mất business logic về trạng thái 'rejected' của hệ thống đặt lịch). </t>
+  </si>
+  <si>
+    <t>hird-party API Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integration (Mentor Booking - Email Notification - `BookMentor.jsx`) </t>
+  </si>
+  <si>
+    <t>Hệ thống cần tự động gửi email thông báo cho Mentor ngay khi ứng viên đặt lịch thành công, bao gồm nội dung trao đổi, thông tin liên lạc và link CV của ứng viên.</t>
+  </si>
+  <si>
+    <t>"How to integrate EmailJS in a React component to send a notification email after a form submission? Provide an async/await try-catch block."</t>
+  </si>
+  <si>
+    <t>AI sinh đoạn mã `emailjs.send()` cơ bản với các tham số Service ID, Template ID tĩnh và một block try-catch in lỗi ra console.</t>
+  </si>
+  <si>
+    <t>Phát hiện nếu service EmailJS bị lỗi mạng hoặc hết quota, tiến trình UI có thể bị treo không chuyển trang được, gây hoang mang cho ứng viên.</t>
+  </si>
+  <si>
+    <t>Tách khối lệnh gửi mail thành một `try...catch` độc lập nằm ngay dưới lệnh Insert Supabase. Nếu gửi mail thất bại, vẫn cho phép chuyển sang trang 'My Bookings'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bắt đối số động từ state React (như `topic`, `booking_time`, và profile `cv_url`) truyền thẳng vào `templateParams` để tự động cá nhân hóa nội dung thư gửi đi. </t>
+  </si>
+  <si>
+    <t>Quyết định sử dụng EmailJS thay vì tự setup Node.js SMTP Backend Server để giảm thiểu chi phí vận hành và phù hợp với mô hình serverless của Supabase</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> No (AI cung cấp đúng template integration chuẩn của EmailJS SDK).</t>
   </si>
 </sst>
 </file>
@@ -460,6 +641,14 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <charset val="0"/>
@@ -470,14 +659,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -975,10 +1156,10 @@
     <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -1122,18 +1303,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1149,13 +1330,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1173,7 +1354,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1228,7 +1409,7 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="75">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -2100,6 +2281,174 @@
         <color rgb="FF000000"/>
       </font>
       <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -2143,11 +2492,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="AI_AuditLog_SWP_Template-style" pivot="0" count="4" xr9:uid="{5A62E572-F47F-4A74-81DC-34D29D03984A}">
-      <tableStyleElement type="wholeTable" dxfId="62"/>
-      <tableStyleElement type="headerRow" dxfId="61"/>
-      <tableStyleElement type="firstRowStripe" dxfId="60"/>
-      <tableStyleElement type="secondRowStripe" dxfId="59"/>
+    <tableStyle name="AI_AuditLog_SWP_Template-style" pivot="0" count="4" xr9:uid="{91F9CFC2-3CCD-47D0-A1EE-DBDC07456AFC}">
+      <tableStyleElement type="wholeTable" dxfId="74"/>
+      <tableStyleElement type="headerRow" dxfId="73"/>
+      <tableStyleElement type="firstRowStripe" dxfId="72"/>
+      <tableStyleElement type="secondRowStripe" dxfId="71"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2252,6 +2601,26 @@
     <tableColumn id="10" name="Human Delta: Decision Ownership" dataDxfId="56"/>
     <tableColumn id="11" name="Evidence" dataDxfId="57"/>
     <tableColumn id="12" name="Hallucination Detected?" dataDxfId="58"/>
+  </tableColumns>
+  <tableStyleInfo name="AI_AuditLog_SWP_Template-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="SWP_34567" displayName="SWP_34567" ref="A1:L4">
+  <tableColumns count="12">
+    <tableColumn id="1" name="Entry #" dataDxfId="59"/>
+    <tableColumn id="2" name="Prompt Type" dataDxfId="60"/>
+    <tableColumn id="3" name="Stage/Component" dataDxfId="61"/>
+    <tableColumn id="4" name="Problem/Context" dataDxfId="62"/>
+    <tableColumn id="5" name="Prompt to AI" dataDxfId="63"/>
+    <tableColumn id="6" name="AI Response (Summary)" dataDxfId="64"/>
+    <tableColumn id="7" name="Human Delta: Critical Thinking" dataDxfId="65"/>
+    <tableColumn id="8" name="Human Delta: Contextualization" dataDxfId="66"/>
+    <tableColumn id="9" name="Human Delta: Creative Synthesis" dataDxfId="67"/>
+    <tableColumn id="10" name="Human Delta: Decision Ownership" dataDxfId="68"/>
+    <tableColumn id="11" name="Evidence" dataDxfId="69"/>
+    <tableColumn id="12" name="Hallucination Detected?" dataDxfId="70"/>
   </tableColumns>
   <tableStyleInfo name="AI_AuditLog_SWP_Template-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2772,19 +3141,19 @@
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="8"/>
-    <col min="2" max="2" width="12.2222222222222" style="8" customWidth="1"/>
-    <col min="3" max="3" width="16.8888888888889" style="8" customWidth="1"/>
-    <col min="4" max="4" width="15.5555555555556" style="8" customWidth="1"/>
-    <col min="5" max="5" width="18" style="8" customWidth="1"/>
-    <col min="6" max="6" width="23.1111111111111" style="8" customWidth="1"/>
-    <col min="7" max="7" width="28.1111111111111" style="8" customWidth="1"/>
-    <col min="8" max="8" width="37.2222222222222" style="8" customWidth="1"/>
-    <col min="9" max="9" width="26.8888888888889" style="8" customWidth="1"/>
-    <col min="10" max="10" width="37.4444444444444" style="8" customWidth="1"/>
-    <col min="11" max="11" width="55.3333333333333" style="8" customWidth="1"/>
-    <col min="12" max="12" width="21.8888888888889" style="8" customWidth="1"/>
-    <col min="13" max="16384" width="8.88888888888889" style="8"/>
+    <col min="1" max="1" width="8.88888888888889" style="9"/>
+    <col min="2" max="2" width="12.2222222222222" style="9" customWidth="1"/>
+    <col min="3" max="3" width="16.8888888888889" style="9" customWidth="1"/>
+    <col min="4" max="4" width="15.5555555555556" style="9" customWidth="1"/>
+    <col min="5" max="5" width="18" style="9" customWidth="1"/>
+    <col min="6" max="6" width="23.1111111111111" style="9" customWidth="1"/>
+    <col min="7" max="7" width="28.1111111111111" style="9" customWidth="1"/>
+    <col min="8" max="8" width="37.2222222222222" style="9" customWidth="1"/>
+    <col min="9" max="9" width="26.8888888888889" style="9" customWidth="1"/>
+    <col min="10" max="10" width="37.4444444444444" style="9" customWidth="1"/>
+    <col min="11" max="11" width="55.3333333333333" style="9" customWidth="1"/>
+    <col min="12" max="12" width="21.8888888888889" style="9" customWidth="1"/>
+    <col min="13" max="16384" width="8.88888888888889" style="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.4" spans="1:12">
@@ -2856,7 +3225,7 @@
       <c r="J2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="6" t="s">
         <v>43</v>
       </c>
       <c r="L2" s="3" t="s">
@@ -2894,7 +3263,7 @@
       <c r="J3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>43</v>
       </c>
       <c r="L3" s="3" t="s">
@@ -2902,37 +3271,37 @@
       </c>
     </row>
     <row r="4" ht="73" customHeight="1" spans="1:12">
-      <c r="A4" s="7">
+      <c r="A4" s="8">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>43</v>
       </c>
       <c r="L4" s="3" t="s">
@@ -3047,7 +3416,7 @@
       <c r="J2" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="7" t="s">
         <v>43</v>
       </c>
       <c r="L2" s="3" t="s">
@@ -3085,7 +3454,7 @@
       <c r="J3" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>43</v>
       </c>
       <c r="L3" s="3" t="s">
@@ -3093,37 +3462,37 @@
       </c>
     </row>
     <row r="4" ht="65" customHeight="1" spans="1:12">
-      <c r="A4" s="7">
+      <c r="A4" s="8">
         <v>9</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>43</v>
       </c>
       <c r="L4" s="3" t="s">
@@ -3239,7 +3608,7 @@
       <c r="J2" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="7" t="s">
         <v>43</v>
       </c>
       <c r="L2" s="3" t="s">
@@ -3277,7 +3646,7 @@
       <c r="J3" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>43</v>
       </c>
       <c r="L3" s="3" t="s">
@@ -3285,37 +3654,37 @@
       </c>
     </row>
     <row r="4" ht="99" customHeight="1" spans="1:12">
-      <c r="A4" s="7">
+      <c r="A4" s="8">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>43</v>
       </c>
       <c r="L4" s="3" t="s">
@@ -3339,4 +3708,313 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="6"/>
+  <cols>
+    <col min="1" max="1" width="8.88888888888889" style="1"/>
+    <col min="2" max="2" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7777777777778" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.4444444444444" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.6666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="28.6666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="29.3333333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24.4444444444444" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.5555555555556" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24.8888888888889" style="1" customWidth="1"/>
+    <col min="12" max="12" width="35.1111111111111" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88888888888889" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="26.4" spans="1:12">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="97" customHeight="1" spans="1:12">
+      <c r="A2" s="4">
+        <v>13</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="109" customHeight="1" spans="1:12">
+      <c r="A3" s="3">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="114" customHeight="1" spans="1:12">
+      <c r="A4" s="8">
+        <v>15</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="114" customHeight="1" spans="1:12">
+      <c r="A5" s="8">
+        <v>16</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="114" customHeight="1" spans="1:12">
+      <c r="A6" s="8">
+        <v>17</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="114" customHeight="1" spans="1:12">
+      <c r="A7" s="8">
+        <v>18</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" sqref="A5 A6 A7 A2:A4">
+      <formula1>AND(ISNUMBER(A2),(NOT(OR(NOT(ISERROR(DATEVALUE(A2))),AND(ISNUMBER(A2),LEFT(CELL("format",A2))="D")))))</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+    <hyperlink ref="K3" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+    <hyperlink ref="K4" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+    <hyperlink ref="K5" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+    <hyperlink ref="K6" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+    <hyperlink ref="K7" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/AI_AuditLog_SWP_NguyenAnhMinh_DE190975.xlsx
+++ b/AI_AuditLog_SWP_NguyenAnhMinh_DE190975.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="5"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="Week 4" sheetId="4" r:id="rId4"/>
     <sheet name="Week 5" sheetId="5" r:id="rId5"/>
     <sheet name="Week 6" sheetId="6" r:id="rId6"/>
+    <sheet name="Week 7" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="223">
   <si>
     <t>Entry #</t>
   </si>
@@ -611,6 +612,96 @@
   </si>
   <si>
     <t xml:space="preserve"> No (AI cung cấp đúng template integration chuẩn của EmailJS SDK).</t>
+  </si>
+  <si>
+    <t>Component State Logic &amp; Edge Cases</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implementation (CV Analysis - Mismatch Warning - `CVManager.jsx`)</t>
+  </si>
+  <si>
+    <t>Tình trạng "bình cũ rượu mới": Khi chọn một vị trí ứng tuyển khác trong dropdown, hệ thống chỉ đổi tên vị trí hiển thị nhưng vẫn giữ nguyên điểm số AI đã phân tích cho vị trí cũ.</t>
+  </si>
+  <si>
+    <t>"In React, how do I show a warning if the currently selected dropdown option (selectedPosition) is different from the position the data was originally evaluated for (evaluatedPositionId)?"</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AI đề xuất so sánh `selectedPosition.id !== analysisResult.evaluatedPositionId` và dùng toán tử ba ngôi (ternary operator) để render một dòng text cảnh báo nhỏ.</t>
+  </si>
+  <si>
+    <t>Nhận thấy một dòng text nhỏ là chưa đủ "đô" với một quy trình HR khắt khe. Trải nghiệm người dùng cần phải rõ ràng để họ hiểu vì sao điểm số không còn hợp lệ.</t>
+  </si>
+  <si>
+    <t>Bổ sung thẻ cảnh báo (Mismatch Warning) nguyên khối màu cam cực kỳ nổi bật với icon `AlertCircle` ngay phía trên thẻ điểm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ghim cố định tên vị trí cũ (`displayPosName`) đi kèm với điểm số hiện tại, đồng thời giải thích rõ ràng lý do hệ thống cảnh báo (VD: "Điểm 80 bên dưới là của Backend. Bạn vừa chọn AI Engineer..."). </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Thiết kế lại hoàn toàn tư duy luồng UI: Thay vì tự động load lại trang, bắt người dùng phải đưa ra quyết định chủ động thông qua nút "Phân tích lại".</t>
+  </si>
+  <si>
+    <t>No (AI cung cấp đúng logic so sánh ID trong React).</t>
+  </si>
+  <si>
+    <t>File System &amp; Network API</t>
+  </si>
+  <si>
+    <t>Implementation (CV Analysis - Re-Analyze &amp; File Rehydration - `CVManager.jsx`)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Để phân tích lại CV (Re-analyze) cho vị trí mới, hệ thống cần gửi lại đối tượng `File` cho hàm AI. Tuy nhiên, nếu user F5 trang, đối tượng `localFile` bị mất, chỉ còn URL từ Supabase.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"How do I convert a file URL back into a JavaScript File object so I can pass it to an upload/analysis function in React?" </t>
+  </si>
+  <si>
+    <t>AI hướng dẫn dùng `fetch(url)` để lấy Response, sau đó gọi `await response.blob()` và khởi tạo `new File([blob], filename)`.</t>
+  </si>
+  <si>
+    <t>Nếu URL bị lỗi hoặc file đã bị xoá trên Supabase Storage, lệnh fetch sẽ văng lỗi (throw error) làm sập hàm phân tích.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đưa khối lệnh fetch file vào một block `try...catch` riêng biệt. Cập nhật UI trạng thái "Đang tải file từ server..." trước khi hiển thị "Bắt đầu phân tích lại...". </t>
+  </si>
+  <si>
+    <t>Tích hợp thẳng hàm gọi DB `updateCVAnalysis` vào luồng Re-analyze để sau khi AI trả kết quả mới, dữ liệu DB của file đó tự động được ghi đè (override) luôn.</t>
+  </si>
+  <si>
+    <t>Chấp nhận tốn thêm băng thông (bandwidth) tải lại file từ server để đánh đổi lấy sự chính xác tuyệt đối của AI cho từng vị trí ứng tuyển cụ thể.</t>
+  </si>
+  <si>
+    <t>No (AI hướng dẫn chuẩn kỹ thuật chuyển đổi Blob thành File).</t>
+  </si>
+  <si>
+    <t>UI Component &amp; Data Visualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implementation (CV Dashboard - `ATSScoreRing` in `CVManager.jsx`)</t>
+  </si>
+  <si>
+    <t>Cần một vòng tròn hiển thị điểm (Score Ring) sinh động thay vì con số khô khan, nhưng điểm số nằm ngoài luồng render chính của file SVG nên khó truyền tham số động.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Create an SVG ring chart component in React that takes a 'score' prop (0-100) and fills the circle border stroke accordingly." </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AI dùng công thức tính `circumference = 2 * Math.PI * radius` và cập nhật `strokeDashoffset` dựa trên số điểm truyền vào.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vòng tròn AI sinh ra chỉ có một màu đơn điệu, không phản ánh được mức độ "Đạt/Chưa đạt". Cần thay đổi linh hoạt theo thang điểm. </t>
+  </si>
+  <si>
+    <t>Định nghĩa 3 dải màu `linearGradient` (High, Medium, Low) ngay trong thẻ `&lt;defs&gt;` của SVG và viết hàm nội suy áp dụng đúng ID gradient tương ứng với điểm.</t>
+  </si>
+  <si>
+    <t>Tách SVG ring ra thành một Functional Component độc lập (`ATSScoreRing`) đặt ngay trong file `CVManager.jsx` để dễ tái sử dụng cho cả ATS Score lẫn Job Match Score.</t>
+  </si>
+  <si>
+    <t>Bỏ qua các thư viện biểu đồ nặng nề như Recharts hay Chart.js, chọn dùng SVG thuần (Vanilla SVG) để đảm bảo trang CV Manager load nhẹ nhất có thể.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No (Toán học tính chu vi và stroke-dashoffset của AI cực kỳ chính xác). </t>
   </si>
 </sst>
 </file>
@@ -1286,7 +1377,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1302,6 +1393,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1409,7 +1503,7 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="75">
+  <dxfs count="87">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -2281,6 +2375,174 @@
         <color rgb="FF000000"/>
       </font>
       <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -2492,11 +2754,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="AI_AuditLog_SWP_Template-style" pivot="0" count="4" xr9:uid="{91F9CFC2-3CCD-47D0-A1EE-DBDC07456AFC}">
-      <tableStyleElement type="wholeTable" dxfId="74"/>
-      <tableStyleElement type="headerRow" dxfId="73"/>
-      <tableStyleElement type="firstRowStripe" dxfId="72"/>
-      <tableStyleElement type="secondRowStripe" dxfId="71"/>
+    <tableStyle name="AI_AuditLog_SWP_Template-style" pivot="0" count="4" xr9:uid="{2EAE5CEE-2121-4A22-B5C8-3BEA20E6D039}">
+      <tableStyleElement type="wholeTable" dxfId="86"/>
+      <tableStyleElement type="headerRow" dxfId="85"/>
+      <tableStyleElement type="firstRowStripe" dxfId="84"/>
+      <tableStyleElement type="secondRowStripe" dxfId="83"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2621,6 +2883,26 @@
     <tableColumn id="10" name="Human Delta: Decision Ownership" dataDxfId="68"/>
     <tableColumn id="11" name="Evidence" dataDxfId="69"/>
     <tableColumn id="12" name="Hallucination Detected?" dataDxfId="70"/>
+  </tableColumns>
+  <tableStyleInfo name="AI_AuditLog_SWP_Template-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="SWP_345678" displayName="SWP_345678" ref="A1:L4">
+  <tableColumns count="12">
+    <tableColumn id="1" name="Entry #" dataDxfId="71"/>
+    <tableColumn id="2" name="Prompt Type" dataDxfId="72"/>
+    <tableColumn id="3" name="Stage/Component" dataDxfId="73"/>
+    <tableColumn id="4" name="Problem/Context" dataDxfId="74"/>
+    <tableColumn id="5" name="Prompt to AI" dataDxfId="75"/>
+    <tableColumn id="6" name="AI Response (Summary)" dataDxfId="76"/>
+    <tableColumn id="7" name="Human Delta: Critical Thinking" dataDxfId="77"/>
+    <tableColumn id="8" name="Human Delta: Contextualization" dataDxfId="78"/>
+    <tableColumn id="9" name="Human Delta: Creative Synthesis" dataDxfId="79"/>
+    <tableColumn id="10" name="Human Delta: Decision Ownership" dataDxfId="80"/>
+    <tableColumn id="11" name="Evidence" dataDxfId="81"/>
+    <tableColumn id="12" name="Hallucination Detected?" dataDxfId="82"/>
   </tableColumns>
   <tableStyleInfo name="AI_AuditLog_SWP_Template-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2843,102 +3125,102 @@
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:11">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="19" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" ht="132" customHeight="1" spans="1:11">
-      <c r="A2" s="19">
+      <c r="A2" s="20">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="22" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1" spans="1:11">
-      <c r="A3" s="22"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:11">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23" t="s">
+      <c r="A4" s="24"/>
+      <c r="B4" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
     </row>
     <row r="5" ht="22.5" customHeight="1"/>
     <row r="6" ht="22.5" customHeight="1"/>
@@ -2986,44 +3268,44 @@
     <col min="9" max="9" width="46.1111111111111" customWidth="1"/>
     <col min="10" max="10" width="30.5555555555556" customWidth="1"/>
     <col min="11" max="11" width="34.2222222222222" customWidth="1"/>
-    <col min="12" max="12" width="20.6666666666667" style="10" customWidth="1"/>
+    <col min="12" max="12" width="20.6666666666667" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="13" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3031,37 +3313,37 @@
       <c r="A2" s="4">
         <v>2</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="13" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3069,53 +3351,53 @@
       <c r="A3" s="3">
         <v>3</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="13" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="12"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="13"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3141,19 +3423,19 @@
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="9"/>
-    <col min="2" max="2" width="12.2222222222222" style="9" customWidth="1"/>
-    <col min="3" max="3" width="16.8888888888889" style="9" customWidth="1"/>
-    <col min="4" max="4" width="15.5555555555556" style="9" customWidth="1"/>
-    <col min="5" max="5" width="18" style="9" customWidth="1"/>
-    <col min="6" max="6" width="23.1111111111111" style="9" customWidth="1"/>
-    <col min="7" max="7" width="28.1111111111111" style="9" customWidth="1"/>
-    <col min="8" max="8" width="37.2222222222222" style="9" customWidth="1"/>
-    <col min="9" max="9" width="26.8888888888889" style="9" customWidth="1"/>
-    <col min="10" max="10" width="37.4444444444444" style="9" customWidth="1"/>
-    <col min="11" max="11" width="55.3333333333333" style="9" customWidth="1"/>
-    <col min="12" max="12" width="21.8888888888889" style="9" customWidth="1"/>
-    <col min="13" max="16384" width="8.88888888888889" style="9"/>
+    <col min="1" max="1" width="8.88888888888889" style="10"/>
+    <col min="2" max="2" width="12.2222222222222" style="10" customWidth="1"/>
+    <col min="3" max="3" width="16.8888888888889" style="10" customWidth="1"/>
+    <col min="4" max="4" width="15.5555555555556" style="10" customWidth="1"/>
+    <col min="5" max="5" width="18" style="10" customWidth="1"/>
+    <col min="6" max="6" width="23.1111111111111" style="10" customWidth="1"/>
+    <col min="7" max="7" width="28.1111111111111" style="10" customWidth="1"/>
+    <col min="8" max="8" width="37.2222222222222" style="10" customWidth="1"/>
+    <col min="9" max="9" width="26.8888888888889" style="10" customWidth="1"/>
+    <col min="10" max="10" width="37.4444444444444" style="10" customWidth="1"/>
+    <col min="11" max="11" width="55.3333333333333" style="10" customWidth="1"/>
+    <col min="12" max="12" width="21.8888888888889" style="10" customWidth="1"/>
+    <col min="13" max="16384" width="8.88888888888889" style="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.4" spans="1:12">
@@ -3225,7 +3507,7 @@
       <c r="J2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="7" t="s">
         <v>43</v>
       </c>
       <c r="L2" s="3" t="s">
@@ -3263,7 +3545,7 @@
       <c r="J3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="8" t="s">
         <v>43</v>
       </c>
       <c r="L3" s="3" t="s">
@@ -3271,37 +3553,37 @@
       </c>
     </row>
     <row r="4" ht="73" customHeight="1" spans="1:12">
-      <c r="A4" s="8">
+      <c r="A4" s="9">
         <v>6</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="8" t="s">
         <v>43</v>
       </c>
       <c r="L4" s="3" t="s">
@@ -3416,7 +3698,7 @@
       <c r="J2" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="8" t="s">
         <v>43</v>
       </c>
       <c r="L2" s="3" t="s">
@@ -3454,7 +3736,7 @@
       <c r="J3" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="8" t="s">
         <v>43</v>
       </c>
       <c r="L3" s="3" t="s">
@@ -3462,37 +3744,37 @@
       </c>
     </row>
     <row r="4" ht="65" customHeight="1" spans="1:12">
-      <c r="A4" s="8">
+      <c r="A4" s="9">
         <v>9</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="8" t="s">
         <v>43</v>
       </c>
       <c r="L4" s="3" t="s">
@@ -3608,7 +3890,7 @@
       <c r="J2" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="8" t="s">
         <v>43</v>
       </c>
       <c r="L2" s="3" t="s">
@@ -3646,7 +3928,7 @@
       <c r="J3" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="8" t="s">
         <v>43</v>
       </c>
       <c r="L3" s="3" t="s">
@@ -3654,37 +3936,37 @@
       </c>
     </row>
     <row r="4" ht="99" customHeight="1" spans="1:12">
-      <c r="A4" s="8">
+      <c r="A4" s="9">
         <v>12</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="8" t="s">
         <v>43</v>
       </c>
       <c r="L4" s="3" t="s">
@@ -3800,7 +4082,7 @@
       <c r="J2" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="7" t="s">
         <v>43</v>
       </c>
       <c r="L2" s="3" t="s">
@@ -3838,7 +4120,7 @@
       <c r="J3" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="8" t="s">
         <v>43</v>
       </c>
       <c r="L3" s="3" t="s">
@@ -3846,37 +4128,37 @@
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="114" customHeight="1" spans="1:12">
-      <c r="A4" s="8">
+      <c r="A4" s="9">
         <v>15</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>43</v>
       </c>
       <c r="L4" s="3" t="s">
@@ -3884,37 +4166,37 @@
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="114" customHeight="1" spans="1:12">
-      <c r="A5" s="8">
+      <c r="A5" s="9">
         <v>16</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>43</v>
       </c>
       <c r="L5" s="3" t="s">
@@ -3922,37 +4204,37 @@
       </c>
     </row>
     <row r="6" s="1" customFormat="1" ht="114" customHeight="1" spans="1:12">
-      <c r="A6" s="8">
+      <c r="A6" s="9">
         <v>17</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="7" t="s">
         <v>43</v>
       </c>
       <c r="L6" s="3" t="s">
@@ -3960,37 +4242,37 @@
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="114" customHeight="1" spans="1:12">
-      <c r="A7" s="8">
+      <c r="A7" s="9">
         <v>18</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
       <c r="L7" s="3" t="s">
@@ -3999,7 +4281,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" sqref="A5 A6 A7 A2:A4">
+    <dataValidation type="custom" allowBlank="1" sqref="A2:A7">
       <formula1>AND(ISNUMBER(A2),(NOT(OR(NOT(ISERROR(DATEVALUE(A2))),AND(ISNUMBER(A2),LEFT(CELL("format",A2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
@@ -4017,4 +4299,199 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="6"/>
+  <cols>
+    <col min="1" max="1" width="8.88888888888889" style="1"/>
+    <col min="2" max="2" width="16.2222222222222" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7777777777778" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5555555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.4444444444444" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.6666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="28.6666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="29.3333333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24.4444444444444" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.5555555555556" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24.8888888888889" style="1" customWidth="1"/>
+    <col min="12" max="12" width="35.1111111111111" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88888888888889" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="26.4" spans="1:12">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="162" customHeight="1" spans="1:12">
+      <c r="A2" s="4">
+        <v>20</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="109" customHeight="1" spans="1:12">
+      <c r="A3" s="4">
+        <v>21</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="114" customHeight="1" spans="1:12">
+      <c r="A4" s="4">
+        <v>22</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="114" customHeight="1"/>
+    <row r="6" s="1" customFormat="1" ht="114" customHeight="1"/>
+    <row r="7" s="1" customFormat="1" ht="114" customHeight="1"/>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" sqref="A2:A4">
+      <formula1>AND(ISNUMBER(A2),(NOT(OR(NOT(ISERROR(DATEVALUE(A2))),AND(ISNUMBER(A2),LEFT(CELL("format",A2))="D")))))</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+    <hyperlink ref="K3" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+    <hyperlink ref="K4" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/AI_AuditLog_SWP_NguyenAnhMinh_DE190975.xlsx
+++ b/AI_AuditLog_SWP_NguyenAnhMinh_DE190975.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="6"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -14,6 +14,7 @@
     <sheet name="Week 5" sheetId="5" r:id="rId5"/>
     <sheet name="Week 6" sheetId="6" r:id="rId6"/>
     <sheet name="Week 7" sheetId="7" r:id="rId7"/>
+    <sheet name="Week 8" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="253">
   <si>
     <t>Entry #</t>
   </si>
@@ -702,6 +703,96 @@
   </si>
   <si>
     <t xml:space="preserve">No (Toán học tính chu vi và stroke-dashoffset của AI cực kỳ chính xác). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generative AI SDK Integration &amp; Error Handling </t>
+  </si>
+  <si>
+    <t>Implementation (CV Analysis - `cvAnalysisService.js`)</t>
+  </si>
+  <si>
+    <t>Trong quá trình phân tích CV, Google Gemini thỉnh thoảng báo lỗi 429 (Rate Limit) hoặc 503 (Overloaded) làm luồng phân tích bị đứt gãy hoàn toàn.</t>
+  </si>
+  <si>
+    <t>"How do I implement exponential backoff and retry logic when calling the Google Gemini API to handle 429 Too Many Requests and 503 Service Unavailable errors?"</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AI cung cấp đoạn code dùng `setTimeout` trong một vòng lặp `while` hoặc `for`, kiểm tra mã lỗi và nhân đôi thời gian chờ (exponential backoff) sau mỗi lần thử lại.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AI khuyên thử lại (retry) vô hạn hoặc quá nhiều lần trên cùng 1 model, điều này sẽ làm UI bị treo (spinning) quá lâu khiến người dùng bỏ đi.</t>
+  </si>
+  <si>
+    <t>Cấu trúc lại vòng lặp: Chỉ retry tối đa 2 lần cho mỗi model, và tuỳ chỉnh thời gian delay `5000 * attempt` (5s -&gt; 10s) hiển thị log rõ ràng trước khi quyết định bỏ cuộc.</t>
+  </si>
+  <si>
+    <t>Tự thiết lập mảng ưu tiên Model (Waterfall fallback): Thử `gemini-3.5-flash` trước, nếu sập hoặc không tồn tại (404), tự động rớt xuống `gemini-2.5-flash` và cuối cùng là `gemini-flash-latest`.</t>
+  </si>
+  <si>
+    <t>Chuyển đổi SDK từ thư viện cũ sang `@google/genai` mới nhất để tận dụng API ổn định hơn, đồng thời tự kiểm soát hoàn toàn flow xử lý lỗi thay vì phó mặc cho SDK.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> No (AI cung cấp đúng pattern Exponential Backoff phổ biến).</t>
+  </si>
+  <si>
+    <t>System Architecture &amp; High Availability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementation (API Key Management - `cvAnalysisService.js`) </t>
+  </si>
+  <si>
+    <t>Ngay cả khi có retry, nếu sử dụng một API key duy nhất của gói Free Tier, hệ thống vẫn sẽ cạn kiệt Quota rất nhanh khi có nhiều user chấm CV cùng lúc.</t>
+  </si>
+  <si>
+    <t>"Write a JavaScript function to implement a round-robin rotation over an array of API keys so that each request uses the next available key."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI viết một hàm dùng biến đếm global `currentIndex` và toán tử chia lấy dư `%` để xoay vòng qua mảng danh sách các chuỗi API Key. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Logic xoay vòng (Round-Robin) của AI đúng nhưng chưa xử lý rủi ro nếu một key trong mảng bị "die" hoặc Rate Limit (429) cứng ngắc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Áp dụng logic xoay vòng vào ngay trong vòng lặp Try-Catch của hàm `callGeminiAnalysis`. Nếu một key bị lỗi 429, hệ thống không chỉ đợi mà còn có thể "nhảy" sang key tiếp theo.</t>
+  </si>
+  <si>
+    <t>Khai báo 5 biến môi trường (`VITE_GEMINI_API_KEY_1` -&gt; `5`) trong file `.env` và tự động gom (filter) những key hợp lệ vào một mảng `GEMINI_KEYS` lúc ứng dụng khởi động.</t>
+  </si>
+  <si>
+    <t>Đưa biến đếm `_geminiKeyIndex` ra phạm vi Global Module để mọi lượt request từ các người dùng khác nhau đều tịnh tiến xoay vòng chung, chia đều tải (load balancing) cho các key.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No (AI cung cấp toán học Modulo `%` chính xác cho Round-Robin). </t>
+  </si>
+  <si>
+    <t>Multi-Model Fallback &amp; Resilience</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementation (Cross-LLM Architecture - `cvAnalysisService.js`) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rủi ro sập toàn bộ hệ thống (Single Point of Failure): Nếu server của Google Gemini sập hoàn toàn ở Châu Á, tính năng cốt lõi chấm CV của dự án sẽ chết đứng.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"How to structure a fallback mechanism in Node.js/React where if the primary AI provider (Gemini) fails entirely, the system automatically calls a secondary AI provider (Groq/Llama)?" </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AI đưa ra mô hình try-catch lồng nhau: `try { callGemini() } catch { callGroq() }`, và cung cấp hàm gọi API Groq bằng `fetch` chuẩn.</t>
+  </si>
+  <si>
+    <t>Việc chuyển từ Gemini sang Llama 3.3 (Groq) đòi hỏi Prompt phải tương thích. Groq Llama không nhận file PDF base64 trực tiếp như Gemini, nó chỉ đọc được Text thuần.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Thiết lập logic rẽ nhánh thông minh: Dùng hàm `extractTextFromFile` (mammoth/pdf.js) để bóc tách Text trước. Nếu Gemini sập, ném chuỗi Text (limit 12,000 ký tự) sang hàm `callGroqAnalysis` kèm theo cùng một System Prompt chuẩn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tích hợp thêm cả hệ thống quản lý Multi-key (Round-robin) tương tự cho mảng `GROQ_KEYS`, đảm bảo dự phòng 2 lớp siêu vững chắc (Gemini x5 keys -&gt; Llama x5 keys -&gt; Local Rule-based). </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Quyết định tích hợp Llama 3.3 Versatile qua Groq API vì tốc độ sinh text của nó cực nhanh (hàng trăm tokens/giây), mang lại trải nghiệm Fallback mượt mà như không hề có lỗi xảy ra.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> No (Cấu trúc try-catch fallback cơ bản AI sinh ra là đúng và dễ hiểu).</t>
   </si>
 </sst>
 </file>
@@ -738,18 +829,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1247,7 +1338,7 @@
     <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1379,15 +1470,15 @@
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1400,10 +1491,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1427,10 +1518,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1448,7 +1539,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1503,7 +1594,7 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="87">
+  <dxfs count="99">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -2375,6 +2466,174 @@
         <color rgb="FF000000"/>
       </font>
       <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -2754,11 +3013,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="AI_AuditLog_SWP_Template-style" pivot="0" count="4" xr9:uid="{2EAE5CEE-2121-4A22-B5C8-3BEA20E6D039}">
-      <tableStyleElement type="wholeTable" dxfId="86"/>
-      <tableStyleElement type="headerRow" dxfId="85"/>
-      <tableStyleElement type="firstRowStripe" dxfId="84"/>
-      <tableStyleElement type="secondRowStripe" dxfId="83"/>
+    <tableStyle name="AI_AuditLog_SWP_Template-style" pivot="0" count="4" xr9:uid="{66674EFA-5461-4A16-9642-2C65AE51425D}">
+      <tableStyleElement type="wholeTable" dxfId="98"/>
+      <tableStyleElement type="headerRow" dxfId="97"/>
+      <tableStyleElement type="firstRowStripe" dxfId="96"/>
+      <tableStyleElement type="secondRowStripe" dxfId="95"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2903,6 +3162,26 @@
     <tableColumn id="10" name="Human Delta: Decision Ownership" dataDxfId="80"/>
     <tableColumn id="11" name="Evidence" dataDxfId="81"/>
     <tableColumn id="12" name="Hallucination Detected?" dataDxfId="82"/>
+  </tableColumns>
+  <tableStyleInfo name="AI_AuditLog_SWP_Template-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="SWP_3456789" displayName="SWP_3456789" ref="A1:L4">
+  <tableColumns count="12">
+    <tableColumn id="1" name="Entry #" dataDxfId="83"/>
+    <tableColumn id="2" name="Prompt Type" dataDxfId="84"/>
+    <tableColumn id="3" name="Stage/Component" dataDxfId="85"/>
+    <tableColumn id="4" name="Problem/Context" dataDxfId="86"/>
+    <tableColumn id="5" name="Prompt to AI" dataDxfId="87"/>
+    <tableColumn id="6" name="AI Response (Summary)" dataDxfId="88"/>
+    <tableColumn id="7" name="Human Delta: Critical Thinking" dataDxfId="89"/>
+    <tableColumn id="8" name="Human Delta: Contextualization" dataDxfId="90"/>
+    <tableColumn id="9" name="Human Delta: Creative Synthesis" dataDxfId="91"/>
+    <tableColumn id="10" name="Human Delta: Decision Ownership" dataDxfId="92"/>
+    <tableColumn id="11" name="Evidence" dataDxfId="93"/>
+    <tableColumn id="12" name="Hallucination Detected?" dataDxfId="94"/>
   </tableColumns>
   <tableStyleInfo name="AI_AuditLog_SWP_Template-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3348,7 +3627,7 @@
       </c>
     </row>
     <row r="3" ht="129" customHeight="1" spans="1:12">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>3</v>
       </c>
       <c r="B3" s="13" t="s">
@@ -3439,40 +3718,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="26.4" spans="1:12">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3510,83 +3789,83 @@
       <c r="K2" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="3" ht="70" customHeight="1" spans="1:12">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="4" ht="73" customHeight="1" spans="1:12">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>6</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3630,40 +3909,40 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:12">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3698,86 +3977,86 @@
       <c r="J2" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="3" ht="123" customHeight="1" spans="1:12">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>8</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="4" ht="65" customHeight="1" spans="1:12">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>9</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3806,56 +4085,56 @@
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="16.2222222222222" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.5555555555556" style="1" customWidth="1"/>
-    <col min="5" max="5" width="26.4444444444444" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.6666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="28.6666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="29.3333333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="24.4444444444444" style="1" customWidth="1"/>
-    <col min="10" max="10" width="28.5555555555556" style="1" customWidth="1"/>
-    <col min="11" max="11" width="24.8888888888889" style="1" customWidth="1"/>
-    <col min="12" max="12" width="35.1111111111111" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.88888888888889" style="3"/>
+    <col min="2" max="2" width="16.2222222222222" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.7777777777778" style="3" customWidth="1"/>
+    <col min="4" max="4" width="30.5555555555556" style="3" customWidth="1"/>
+    <col min="5" max="5" width="26.4444444444444" style="3" customWidth="1"/>
+    <col min="6" max="6" width="25.6666666666667" style="3" customWidth="1"/>
+    <col min="7" max="7" width="28.6666666666667" style="3" customWidth="1"/>
+    <col min="8" max="8" width="29.3333333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24.4444444444444" style="3" customWidth="1"/>
+    <col min="10" max="10" width="28.5555555555556" style="3" customWidth="1"/>
+    <col min="11" max="11" width="24.8888888888889" style="3" customWidth="1"/>
+    <col min="12" max="12" width="35.1111111111111" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="8.88888888888889" style="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.4" spans="1:12">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3890,86 +4169,86 @@
       <c r="J2" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="3" ht="79" customHeight="1" spans="1:12">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="4" ht="99" customHeight="1" spans="1:12">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>12</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3998,60 +4277,60 @@
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="16.2222222222222" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.5555555555556" style="1" customWidth="1"/>
-    <col min="5" max="5" width="26.4444444444444" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.6666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="28.6666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="29.3333333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="24.4444444444444" style="1" customWidth="1"/>
-    <col min="10" max="10" width="28.5555555555556" style="1" customWidth="1"/>
-    <col min="11" max="11" width="24.8888888888889" style="1" customWidth="1"/>
-    <col min="12" max="12" width="35.1111111111111" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.88888888888889" style="3"/>
+    <col min="2" max="2" width="16.2222222222222" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.7777777777778" style="3" customWidth="1"/>
+    <col min="4" max="4" width="30.5555555555556" style="3" customWidth="1"/>
+    <col min="5" max="5" width="26.4444444444444" style="3" customWidth="1"/>
+    <col min="6" max="6" width="25.6666666666667" style="3" customWidth="1"/>
+    <col min="7" max="7" width="28.6666666666667" style="3" customWidth="1"/>
+    <col min="8" max="8" width="29.3333333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24.4444444444444" style="3" customWidth="1"/>
+    <col min="10" max="10" width="28.5555555555556" style="3" customWidth="1"/>
+    <col min="11" max="11" width="24.8888888888889" style="3" customWidth="1"/>
+    <col min="12" max="12" width="35.1111111111111" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="8.88888888888889" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="26.4" spans="1:12">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="3" customFormat="1" ht="26.4" spans="1:12">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="97" customHeight="1" spans="1:12">
+    <row r="2" s="3" customFormat="1" ht="97" customHeight="1" spans="1:12">
       <c r="A2" s="4">
         <v>13</v>
       </c>
@@ -4085,197 +4364,197 @@
       <c r="K2" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="109" customHeight="1" spans="1:12">
-      <c r="A3" s="3">
+    <row r="3" s="3" customFormat="1" ht="109" customHeight="1" spans="1:12">
+      <c r="A3" s="2">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="114" customHeight="1" spans="1:12">
-      <c r="A4" s="9">
+    <row r="4" s="3" customFormat="1" ht="114" customHeight="1" spans="1:12">
+      <c r="A4" s="8">
         <v>15</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="8" t="s">
         <v>161</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="114" customHeight="1" spans="1:12">
-      <c r="A5" s="9">
+    <row r="5" s="3" customFormat="1" ht="114" customHeight="1" spans="1:12">
+      <c r="A5" s="8">
         <v>16</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="8" t="s">
         <v>171</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" s="2" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="114" customHeight="1" spans="1:12">
-      <c r="A6" s="9">
+    <row r="6" s="3" customFormat="1" ht="114" customHeight="1" spans="1:12">
+      <c r="A6" s="8">
         <v>17</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="8" t="s">
         <v>181</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="L6" s="2" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="114" customHeight="1" spans="1:12">
-      <c r="A7" s="9">
+    <row r="7" s="3" customFormat="1" ht="114" customHeight="1" spans="1:12">
+      <c r="A7" s="8">
         <v>18</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="8" t="s">
         <v>191</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="L7" s="2" t="s">
         <v>192</v>
       </c>
     </row>
@@ -4307,62 +4586,62 @@
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="8.88888888888889" style="1"/>
-    <col min="2" max="2" width="16.2222222222222" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.5555555555556" style="1" customWidth="1"/>
-    <col min="5" max="5" width="26.4444444444444" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.6666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="28.6666666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="29.3333333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="24.4444444444444" style="1" customWidth="1"/>
-    <col min="10" max="10" width="28.5555555555556" style="1" customWidth="1"/>
-    <col min="11" max="11" width="24.8888888888889" style="1" customWidth="1"/>
-    <col min="12" max="12" width="35.1111111111111" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="8.88888888888889" style="3"/>
+    <col min="2" max="2" width="16.2222222222222" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.7777777777778" style="3" customWidth="1"/>
+    <col min="4" max="4" width="30.5555555555556" style="3" customWidth="1"/>
+    <col min="5" max="5" width="26.4444444444444" style="3" customWidth="1"/>
+    <col min="6" max="6" width="25.6666666666667" style="3" customWidth="1"/>
+    <col min="7" max="7" width="28.6666666666667" style="3" customWidth="1"/>
+    <col min="8" max="8" width="29.3333333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="24.4444444444444" style="3" customWidth="1"/>
+    <col min="10" max="10" width="28.5555555555556" style="3" customWidth="1"/>
+    <col min="11" max="11" width="24.8888888888889" style="3" customWidth="1"/>
+    <col min="12" max="12" width="35.1111111111111" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="8.88888888888889" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="26.4" spans="1:12">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="3" customFormat="1" ht="26.4" spans="1:12">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="162" customHeight="1" spans="1:12">
+    <row r="2" s="3" customFormat="1" ht="162" customHeight="1" spans="1:12">
       <c r="A2" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>193</v>
@@ -4394,89 +4673,89 @@
       <c r="K2" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="109" customHeight="1" spans="1:12">
+    <row r="3" s="3" customFormat="1" ht="109" customHeight="1" spans="1:12">
       <c r="A3" s="4">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" s="3" customFormat="1" ht="114" customHeight="1" spans="1:12">
+      <c r="A4" s="4">
         <v>21</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="114" customHeight="1" spans="1:12">
-      <c r="A4" s="4">
-        <v>22</v>
-      </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="8" t="s">
         <v>221</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="114" customHeight="1"/>
-    <row r="6" s="1" customFormat="1" ht="114" customHeight="1"/>
-    <row r="7" s="1" customFormat="1" ht="114" customHeight="1"/>
+    <row r="5" s="3" customFormat="1" ht="114" customHeight="1"/>
+    <row r="6" s="3" customFormat="1" ht="114" customHeight="1"/>
+    <row r="7" s="3" customFormat="1" ht="114" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" sqref="A2:A4">
@@ -4494,4 +4773,198 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="3"/>
+  <cols>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="20.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="41.2222222222222" customWidth="1"/>
+    <col min="5" max="5" width="58.6666666666667" customWidth="1"/>
+    <col min="6" max="6" width="42" customWidth="1"/>
+    <col min="7" max="7" width="40.7777777777778" customWidth="1"/>
+    <col min="8" max="8" width="29.6666666666667" customWidth="1"/>
+    <col min="9" max="9" width="35.7777777777778" customWidth="1"/>
+    <col min="10" max="10" width="32.8888888888889" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="26.6666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26.4" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="3"/>
+    </row>
+    <row r="2" ht="120" customHeight="1" spans="1:13">
+      <c r="A2" s="4">
+        <v>22</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" ht="79.2" spans="1:13">
+      <c r="A3" s="4">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" ht="104" customHeight="1" spans="1:13">
+      <c r="A4" s="4">
+        <v>24</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="M4" s="3"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" sqref="A2:A4">
+      <formula1>AND(ISNUMBER(A2),(NOT(OR(NOT(ISERROR(DATEVALUE(A2))),AND(ISNUMBER(A2),LEFT(CELL("format",A2))="D")))))</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0" tooltip="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+    <hyperlink ref="K3" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0" tooltip="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+    <hyperlink ref="K4" r:id="rId2" display="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0" tooltip="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/AI_AuditLog_SWP_NguyenAnhMinh_DE190975.xlsx
+++ b/AI_AuditLog_SWP_NguyenAnhMinh_DE190975.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="7"/>
+    <workbookView windowWidth="23040" windowHeight="9000" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -15,6 +15,8 @@
     <sheet name="Week 6" sheetId="6" r:id="rId6"/>
     <sheet name="Week 7" sheetId="7" r:id="rId7"/>
     <sheet name="Week 8" sheetId="8" r:id="rId8"/>
+    <sheet name="Week 9" sheetId="9" r:id="rId9"/>
+    <sheet name="Week 10" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="275">
   <si>
     <t>Entry #</t>
   </si>
@@ -793,6 +795,72 @@
   </si>
   <si>
     <t xml:space="preserve"> No (Cấu trúc try-catch fallback cơ bản AI sinh ra là đúng và dễ hiểu).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI/UX Refactoring &amp; Motion Design Integration </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementation (CV Manager - React JSX Overhaul) </t>
+  </si>
+  <si>
+    <t>Giao diện CV Manager ban đầu quá "flat" và tĩnh lặng: khu vực upload chỉ là viền đứt nét, danh sách CV là list cuộn dài mỏi tay. Cần nâng cấp toàn diện layout lên chuẩn SaaS Premium.</t>
+  </si>
+  <si>
+    <t>Tôi muốn tích hợp thư viện Aceternity UI (Bento Grid, Kinetic Upload) và Framer Motion vào CVManager. Hãy cấu trúc lại phần JSX mà KHÔNG ảnh hưởng đến logic AI phía trên."</t>
+  </si>
+  <si>
+    <t>AI lên kế hoạch: Cài `framer-motion`, `lucide-react`; tái cấu trúc phần JSX cuối file thành Kinetic Upload Portal với Spring Animations (`whileHover`, `whileTap`).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Yêu cầu giữ nguyên 100% hệ màu "Clean Tech" (Kem, Trắng, Xám, Vàng Cát) — bác bỏ đề xuất Dark Mode/Neon mặc định của Aceternity UI. </t>
+  </si>
+  <si>
+    <t>Áp dụng Spring Animations (`type: 'spring', stiffness: 400, damping: 25`) cho Drop Zone. Tái cấu trúc grid hiển thị Bento UI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tự tích hợp Aceternity-style grid background pattern (24px) bằng thẻ SVG inline. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiên quyết chỉ "phẫu thuật" phần vỏ bọc JSX (return statement), giữ nguyên 100% logic AI/Supabase ở phần trên. Xác nhận không ảnh hưởng API integrations. </t>
+  </si>
+  <si>
+    <t>`CVManager.jsx`, `package.json`</t>
+  </si>
+  <si>
+    <t>No (AI tách đúng phần UI ra khỏi logic AI).</t>
+  </si>
+  <si>
+    <t>Advanced Data Visualization &amp; CSS Styling</t>
+  </si>
+  <si>
+    <t>Implementation (CV Manager - CSS &amp; Graphic Elements)</t>
+  </si>
+  <si>
+    <t>File CSS cũ không còn phù hợp với cấu trúc Bento Grid. Cần viết lại toàn bộ CSS, bổ sung các component đồ họa SVG nâng cao (Sparkle Button, ATS Score Ring).</t>
+  </si>
+  <si>
+    <t>"Hãy viết file CSS hoàn chỉnh cho giao diện Bento Grid mới dựa trên hệ màu Clean Tech. Thêm nút Sparkle Button với hiệu ứng particle và vòng tròn ATS Score."</t>
+  </si>
+  <si>
+    <t>AI sinh toàn bộ CSS class tương ứng và code inline SVG cho Sparkle Button (Uiverse) và ATS Ring</t>
+  </si>
+  <si>
+    <t>AI viết code CSS quá dài và đôi chỗ lặp class. Tôi tự cấu trúc lại CSS thành các block BEM rõ ràng để dễ bảo trì.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Định nghĩa lại các thẻ CSS Variables (`--color-cream`, `--color-accent`) ở đầu file để đồng bộ màu sắc toàn trang. </t>
+  </si>
+  <si>
+    <t>Tích hợp Sparkle Button (10 particle effects bằng SVG inline) và ATS Score Ring hiển thị gradient 3 màu siêu mượt.</t>
+  </si>
+  <si>
+    <t>Tự thiết kế các hiệu ứng CSS Shimmer loading cho phần chờ AI phân tích thay vì dùng ảnh GIF để tối ưu hiệu suất.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> `CVManager.css` (2156 dòng)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> No (AI sinh mã CSS và SVG chuẩn xác).</t>
   </si>
 </sst>
 </file>
@@ -1594,7 +1662,7 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="99">
+  <dxfs count="123">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -2793,6 +2861,342 @@
       <font>
         <name val="Arial"/>
         <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="none"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -3013,11 +3417,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="AI_AuditLog_SWP_Template-style" pivot="0" count="4" xr9:uid="{66674EFA-5461-4A16-9642-2C65AE51425D}">
-      <tableStyleElement type="wholeTable" dxfId="98"/>
-      <tableStyleElement type="headerRow" dxfId="97"/>
-      <tableStyleElement type="firstRowStripe" dxfId="96"/>
-      <tableStyleElement type="secondRowStripe" dxfId="95"/>
+    <tableStyle name="AI_AuditLog_SWP_Template-style" pivot="0" count="4" xr9:uid="{36CB1639-94EB-4D64-ADF1-764A90D30A41}">
+      <tableStyleElement type="wholeTable" dxfId="122"/>
+      <tableStyleElement type="headerRow" dxfId="121"/>
+      <tableStyleElement type="firstRowStripe" dxfId="120"/>
+      <tableStyleElement type="secondRowStripe" dxfId="119"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3042,6 +3446,26 @@
     <tableColumn id="9" name="Human Delta: Creative Synthesis" dataDxfId="8"/>
     <tableColumn id="10" name="Human Delta: Decision Ownership" dataDxfId="9"/>
     <tableColumn id="11" name="Evidence" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="AI_AuditLog_SWP_Template-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="SWP_345678911" displayName="SWP_345678911" ref="A1:L4">
+  <tableColumns count="12">
+    <tableColumn id="1" name="Entry #" dataDxfId="107"/>
+    <tableColumn id="2" name="Prompt Type" dataDxfId="108"/>
+    <tableColumn id="3" name="Stage/Component" dataDxfId="109"/>
+    <tableColumn id="4" name="Problem/Context" dataDxfId="110"/>
+    <tableColumn id="5" name="Prompt to AI" dataDxfId="111"/>
+    <tableColumn id="6" name="AI Response (Summary)" dataDxfId="112"/>
+    <tableColumn id="7" name="Human Delta: Critical Thinking" dataDxfId="113"/>
+    <tableColumn id="8" name="Human Delta: Contextualization" dataDxfId="114"/>
+    <tableColumn id="9" name="Human Delta: Creative Synthesis" dataDxfId="115"/>
+    <tableColumn id="10" name="Human Delta: Decision Ownership" dataDxfId="116"/>
+    <tableColumn id="11" name="Evidence" dataDxfId="117"/>
+    <tableColumn id="12" name="Hallucination Detected?" dataDxfId="118"/>
   </tableColumns>
   <tableStyleInfo name="AI_AuditLog_SWP_Template-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3182,6 +3606,26 @@
     <tableColumn id="10" name="Human Delta: Decision Ownership" dataDxfId="92"/>
     <tableColumn id="11" name="Evidence" dataDxfId="93"/>
     <tableColumn id="12" name="Hallucination Detected?" dataDxfId="94"/>
+  </tableColumns>
+  <tableStyleInfo name="AI_AuditLog_SWP_Template-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="SWP_345678910" displayName="SWP_345678910" ref="A1:L2">
+  <tableColumns count="12">
+    <tableColumn id="1" name="Entry #" dataDxfId="95"/>
+    <tableColumn id="2" name="Prompt Type" dataDxfId="96"/>
+    <tableColumn id="3" name="Stage/Component" dataDxfId="97"/>
+    <tableColumn id="4" name="Problem/Context" dataDxfId="98"/>
+    <tableColumn id="5" name="Prompt to AI" dataDxfId="99"/>
+    <tableColumn id="6" name="AI Response (Summary)" dataDxfId="100"/>
+    <tableColumn id="7" name="Human Delta: Critical Thinking" dataDxfId="101"/>
+    <tableColumn id="8" name="Human Delta: Contextualization" dataDxfId="102"/>
+    <tableColumn id="9" name="Human Delta: Creative Synthesis" dataDxfId="103"/>
+    <tableColumn id="10" name="Human Delta: Decision Ownership" dataDxfId="104"/>
+    <tableColumn id="11" name="Evidence" dataDxfId="105"/>
+    <tableColumn id="12" name="Hallucination Detected?" dataDxfId="106"/>
   </tableColumns>
   <tableStyleInfo name="AI_AuditLog_SWP_Template-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3530,6 +3974,147 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="3"/>
+  <cols>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="20.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="41.2222222222222" customWidth="1"/>
+    <col min="5" max="5" width="58.6666666666667" customWidth="1"/>
+    <col min="6" max="6" width="42" customWidth="1"/>
+    <col min="7" max="7" width="40.7777777777778" customWidth="1"/>
+    <col min="8" max="8" width="29.6666666666667" customWidth="1"/>
+    <col min="9" max="9" width="35.7777777777778" customWidth="1"/>
+    <col min="10" max="10" width="32.8888888888889" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="26.6666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="3"/>
+    </row>
+    <row r="2" ht="120" customHeight="1" spans="1:13">
+      <c r="A2" s="4">
+        <v>26</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" ht="13.8" spans="1:13">
+      <c r="A3" s="4"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" ht="88" customHeight="1" spans="1:13">
+      <c r="A4" s="4"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="3"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" sqref="A2:A4">
+      <formula1>AND(ISNUMBER(A2),(NOT(OR(NOT(ISERROR(DATEVALUE(A2))),AND(ISNUMBER(A2),LEFT(CELL("format",A2))="D")))))</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -4794,7 +5379,7 @@
     <col min="12" max="12" width="26.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.4" spans="1:13">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4967,4 +5552,124 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.2" outlineLevelRow="3"/>
+  <cols>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="20.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="41.2222222222222" customWidth="1"/>
+    <col min="5" max="5" width="58.6666666666667" customWidth="1"/>
+    <col min="6" max="6" width="42" customWidth="1"/>
+    <col min="7" max="7" width="40.7777777777778" customWidth="1"/>
+    <col min="8" max="8" width="29.6666666666667" customWidth="1"/>
+    <col min="9" max="9" width="35.7777777777778" customWidth="1"/>
+    <col min="10" max="10" width="32.8888888888889" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="26.6666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="3"/>
+    </row>
+    <row r="2" ht="120" customHeight="1" spans="1:13">
+      <c r="A2" s="4">
+        <v>25</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="M2" s="3"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" ht="104" customHeight="1" spans="1:13">
+      <c r="M4" s="3"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" sqref="A2">
+      <formula1>AND(ISNUMBER(A2),(NOT(OR(NOT(ISERROR(DATEVALUE(A2))),AND(ISNUMBER(A2),LEFT(CELL("format",A2))="D")))))</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId2" display="`CVManager.jsx`, `package.json`" tooltip="https://docs.google.com/document/d/1eKvFwEUnsxnH7yImOXPAc3Zu7ReY_qVXLsTXpP064lI/edit?tab=t.0"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>